--- a/research/traditional_assets/database/data/ghana/ghana_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_telecom_wireless.xlsx
@@ -1191,7 +1191,7 @@
         <v>0.154916517161461</v>
       </c>
       <c r="X2">
-        <v>2.02239407699591</v>
+        <v>2.02239407699592</v>
       </c>
       <c r="Y2">
         <v>0.667343035620258</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1498312672103113</v>
+        <v>0.1494904390422856</v>
       </c>
       <c r="C2">
-        <v>2446.481473266534</v>
+        <v>2429.248839470692</v>
       </c>
       <c r="D2">
-        <v>2334.781473266534</v>
+        <v>2341.556839470692</v>
       </c>
       <c r="E2">
-        <v>-146.9</v>
+        <v>-122.892</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24.008</v>
       </c>
       <c r="G2">
         <v>111.7</v>
@@ -1451,28 +1451,28 @@
         <v>445.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2076024</v>
       </c>
       <c r="N2">
-        <v>445.3</v>
+        <v>444.0923976</v>
       </c>
       <c r="O2">
-        <v>111.325</v>
+        <v>111.0230994</v>
       </c>
       <c r="P2">
-        <v>333.975</v>
+        <v>333.0692982</v>
       </c>
       <c r="Q2">
-        <v>472.775</v>
+        <v>471.8692982000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1498312672103113</v>
+        <v>0.1506193828709955</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6410622972273367</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>368.7471969250806</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1494904390422856</v>
+        <v>0.1491496108742598</v>
       </c>
       <c r="C3">
-        <v>2429.248839470692</v>
+        <v>2412.055643361085</v>
       </c>
       <c r="D3">
-        <v>2341.556839470692</v>
+        <v>2348.371643361085</v>
       </c>
       <c r="E3">
-        <v>-122.892</v>
+        <v>-98.884</v>
       </c>
       <c r="F3">
-        <v>24.008</v>
+        <v>48.01600000000001</v>
       </c>
       <c r="G3">
         <v>111.7</v>
@@ -1533,28 +1533,28 @@
         <v>445.3</v>
       </c>
       <c r="M3">
-        <v>1.2076024</v>
+        <v>2.4152048</v>
       </c>
       <c r="N3">
-        <v>444.0923976</v>
+        <v>442.8847952</v>
       </c>
       <c r="O3">
-        <v>111.0230994</v>
+        <v>110.7211988</v>
       </c>
       <c r="P3">
-        <v>333.0692982</v>
+        <v>332.1635964</v>
       </c>
       <c r="Q3">
-        <v>471.8692982000001</v>
+        <v>470.9635964</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1506193828709955</v>
+        <v>0.1514235825247549</v>
       </c>
       <c r="T3">
-        <v>0.6410622972273367</v>
+        <v>0.6459806821991592</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>368.7471969250806</v>
+        <v>184.3735984625403</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1491496108742598</v>
+        <v>0.148808782706234</v>
       </c>
       <c r="C4">
-        <v>2412.055643361085</v>
+        <v>2394.902230277916</v>
       </c>
       <c r="D4">
-        <v>2348.371643361085</v>
+        <v>2355.226230277916</v>
       </c>
       <c r="E4">
-        <v>-98.884</v>
+        <v>-74.876</v>
       </c>
       <c r="F4">
-        <v>48.01600000000001</v>
+        <v>72.024</v>
       </c>
       <c r="G4">
         <v>111.7</v>
@@ -1615,28 +1615,28 @@
         <v>445.3</v>
       </c>
       <c r="M4">
-        <v>2.4152048</v>
+        <v>3.6228072</v>
       </c>
       <c r="N4">
-        <v>442.8847952</v>
+        <v>441.6771928</v>
       </c>
       <c r="O4">
-        <v>110.7211988</v>
+        <v>110.4192982</v>
       </c>
       <c r="P4">
-        <v>332.1635964</v>
+        <v>331.2578946</v>
       </c>
       <c r="Q4">
-        <v>470.9635964</v>
+        <v>470.0578946</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1514235825247549</v>
+        <v>0.1522443636146742</v>
       </c>
       <c r="T4">
-        <v>0.6459806821991592</v>
+        <v>0.6510004771704004</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>184.3735984625403</v>
+        <v>122.9157323083602</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.148808782706234</v>
+        <v>0.1484679545382082</v>
       </c>
       <c r="C5">
-        <v>2394.902230277916</v>
+        <v>2377.788949605203</v>
       </c>
       <c r="D5">
-        <v>2355.226230277916</v>
+        <v>2362.120949605203</v>
       </c>
       <c r="E5">
-        <v>-74.876</v>
+        <v>-50.86799999999999</v>
       </c>
       <c r="F5">
-        <v>72.024</v>
+        <v>96.03200000000001</v>
       </c>
       <c r="G5">
         <v>111.7</v>
@@ -1697,28 +1697,28 @@
         <v>445.3</v>
       </c>
       <c r="M5">
-        <v>3.6228072</v>
+        <v>4.8304096</v>
       </c>
       <c r="N5">
-        <v>441.6771928</v>
+        <v>440.4695904</v>
       </c>
       <c r="O5">
-        <v>110.4192982</v>
+        <v>110.1173976</v>
       </c>
       <c r="P5">
-        <v>331.2578946</v>
+        <v>330.3521928</v>
       </c>
       <c r="Q5">
-        <v>470.0578946</v>
+        <v>469.1521928</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1522443636146742</v>
+        <v>0.1530822443106336</v>
       </c>
       <c r="T5">
-        <v>0.6510004771704004</v>
+        <v>0.6561248512035428</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>122.9157323083602</v>
+        <v>92.18679923127016</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1484679545382082</v>
+        <v>0.1481271263701825</v>
       </c>
       <c r="C6">
-        <v>2377.788949605203</v>
+        <v>2360.716154830143</v>
       </c>
       <c r="D6">
-        <v>2362.120949605203</v>
+        <v>2369.056154830143</v>
       </c>
       <c r="E6">
-        <v>-50.86799999999999</v>
+        <v>-26.85999999999999</v>
       </c>
       <c r="F6">
-        <v>96.03200000000001</v>
+        <v>120.04</v>
       </c>
       <c r="G6">
         <v>111.7</v>
@@ -1779,28 +1779,28 @@
         <v>445.3</v>
       </c>
       <c r="M6">
-        <v>4.8304096</v>
+        <v>6.038012000000001</v>
       </c>
       <c r="N6">
-        <v>440.4695904</v>
+        <v>439.261988</v>
       </c>
       <c r="O6">
-        <v>110.1173976</v>
+        <v>109.815497</v>
       </c>
       <c r="P6">
-        <v>330.3521928</v>
+        <v>329.446491</v>
       </c>
       <c r="Q6">
-        <v>469.1521928</v>
+        <v>468.246491</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1530822443106336</v>
+        <v>0.1539377646001921</v>
       </c>
       <c r="T6">
-        <v>0.6561248512035428</v>
+        <v>0.6613571067952776</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>92.18679923127016</v>
+        <v>73.74943938501612</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1481271263701825</v>
+        <v>0.1477862982021567</v>
       </c>
       <c r="C7">
-        <v>2360.716154830143</v>
+        <v>2343.684203603516</v>
       </c>
       <c r="D7">
-        <v>2369.056154830143</v>
+        <v>2376.032203603517</v>
       </c>
       <c r="E7">
-        <v>-26.85999999999999</v>
+        <v>-2.851999999999975</v>
       </c>
       <c r="F7">
-        <v>120.04</v>
+        <v>144.048</v>
       </c>
       <c r="G7">
         <v>111.7</v>
@@ -1861,28 +1861,28 @@
         <v>445.3</v>
       </c>
       <c r="M7">
-        <v>6.038012000000001</v>
+        <v>7.245614400000001</v>
       </c>
       <c r="N7">
-        <v>439.261988</v>
+        <v>438.0543856</v>
       </c>
       <c r="O7">
-        <v>109.815497</v>
+        <v>109.5135964</v>
       </c>
       <c r="P7">
-        <v>329.446491</v>
+        <v>328.5407892</v>
       </c>
       <c r="Q7">
-        <v>468.246491</v>
+        <v>467.3407892</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1539377646001921</v>
+        <v>0.1548114874491029</v>
       </c>
       <c r="T7">
-        <v>0.6613571067952776</v>
+        <v>0.6667006869740706</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>73.74943938501612</v>
+        <v>61.4578661541801</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1477862982021567</v>
+        <v>0.1474454700341309</v>
       </c>
       <c r="C8">
-        <v>2343.684203603517</v>
+        <v>2326.693457801181</v>
       </c>
       <c r="D8">
-        <v>2376.032203603517</v>
+        <v>2383.049457801181</v>
       </c>
       <c r="E8">
-        <v>-2.852000000000004</v>
+        <v>21.15599999999998</v>
       </c>
       <c r="F8">
-        <v>144.048</v>
+        <v>168.056</v>
       </c>
       <c r="G8">
         <v>111.7</v>
@@ -1943,28 +1943,28 @@
         <v>445.3</v>
       </c>
       <c r="M8">
-        <v>7.2456144</v>
+        <v>8.453216799999998</v>
       </c>
       <c r="N8">
-        <v>438.0543856</v>
+        <v>436.8467832</v>
       </c>
       <c r="O8">
-        <v>109.5135964</v>
+        <v>109.2116958</v>
       </c>
       <c r="P8">
-        <v>328.5407892</v>
+        <v>327.6350874</v>
       </c>
       <c r="Q8">
-        <v>467.3407892</v>
+        <v>466.4350874</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1548114874491029</v>
+        <v>0.1557040000366999</v>
       </c>
       <c r="T8">
-        <v>0.6667006869740706</v>
+        <v>0.6721591828556333</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>61.4578661541801</v>
+        <v>52.67817098929724</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1474454700341309</v>
+        <v>0.1471046418661051</v>
       </c>
       <c r="C9">
-        <v>2326.693457801182</v>
+        <v>2309.744283586637</v>
       </c>
       <c r="D9">
-        <v>2383.049457801183</v>
+        <v>2390.108283586637</v>
       </c>
       <c r="E9">
-        <v>21.15600000000003</v>
+        <v>45.16400000000002</v>
       </c>
       <c r="F9">
-        <v>168.056</v>
+        <v>192.064</v>
       </c>
       <c r="G9">
         <v>111.7</v>
@@ -2025,28 +2025,28 @@
         <v>445.3</v>
       </c>
       <c r="M9">
-        <v>8.453216800000002</v>
+        <v>9.660819200000001</v>
       </c>
       <c r="N9">
-        <v>436.8467832</v>
+        <v>435.6391808</v>
       </c>
       <c r="O9">
-        <v>109.2116958</v>
+        <v>108.9097952</v>
       </c>
       <c r="P9">
-        <v>327.6350874</v>
+        <v>326.7293856</v>
       </c>
       <c r="Q9">
-        <v>466.4350874</v>
+        <v>465.5293856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1557040000366999</v>
+        <v>0.1566159150718534</v>
       </c>
       <c r="T9">
-        <v>0.6721591828556333</v>
+        <v>0.6777363416911432</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>52.67817098929722</v>
+        <v>46.09339961563508</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1471046418661051</v>
+        <v>0.1467638136980793</v>
       </c>
       <c r="C10">
-        <v>2309.744283586637</v>
+        <v>2292.837051474725</v>
       </c>
       <c r="D10">
-        <v>2390.108283586637</v>
+        <v>2397.209051474725</v>
       </c>
       <c r="E10">
-        <v>45.16400000000002</v>
+        <v>69.172</v>
       </c>
       <c r="F10">
-        <v>192.064</v>
+        <v>216.072</v>
       </c>
       <c r="G10">
         <v>111.7</v>
@@ -2107,28 +2107,28 @@
         <v>445.3</v>
       </c>
       <c r="M10">
-        <v>9.660819200000001</v>
+        <v>10.8684216</v>
       </c>
       <c r="N10">
-        <v>435.6391808</v>
+        <v>434.4315784</v>
       </c>
       <c r="O10">
-        <v>108.9097952</v>
+        <v>108.6078946</v>
       </c>
       <c r="P10">
-        <v>326.7293856</v>
+        <v>325.8236838</v>
       </c>
       <c r="Q10">
-        <v>465.5293856</v>
+        <v>464.6236838</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1566159150718534</v>
+        <v>0.1575478721956916</v>
       </c>
       <c r="T10">
-        <v>0.6777363416911432</v>
+        <v>0.6834360754461145</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>46.09339961563508</v>
+        <v>40.97191076945341</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1467638136980793</v>
+        <v>0.1464229855300536</v>
       </c>
       <c r="C11">
-        <v>2292.837051474725</v>
+        <v>2275.972136396449</v>
       </c>
       <c r="D11">
-        <v>2397.209051474725</v>
+        <v>2404.352136396449</v>
       </c>
       <c r="E11">
-        <v>69.172</v>
+        <v>93.17999999999998</v>
       </c>
       <c r="F11">
-        <v>216.072</v>
+        <v>240.08</v>
       </c>
       <c r="G11">
         <v>111.7</v>
@@ -2189,28 +2189,28 @@
         <v>445.3</v>
       </c>
       <c r="M11">
-        <v>10.8684216</v>
+        <v>12.076024</v>
       </c>
       <c r="N11">
-        <v>434.4315784</v>
+        <v>433.223976</v>
       </c>
       <c r="O11">
-        <v>108.6078946</v>
+        <v>108.305994</v>
       </c>
       <c r="P11">
-        <v>325.8236838</v>
+        <v>324.917982</v>
       </c>
       <c r="Q11">
-        <v>464.6236838</v>
+        <v>463.717982</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1575478721956916</v>
+        <v>0.1585005394778373</v>
       </c>
       <c r="T11">
-        <v>0.6834360754461145</v>
+        <v>0.6892624699511964</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.97191076945341</v>
+        <v>36.87471969250807</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1464229855300536</v>
+        <v>0.1460821573620278</v>
       </c>
       <c r="C12">
-        <v>2275.972136396449</v>
+        <v>2259.149917764978</v>
       </c>
       <c r="D12">
-        <v>2404.352136396449</v>
+        <v>2411.537917764978</v>
       </c>
       <c r="E12">
-        <v>93.18000000000004</v>
+        <v>117.188</v>
       </c>
       <c r="F12">
-        <v>240.08</v>
+        <v>264.088</v>
       </c>
       <c r="G12">
         <v>111.7</v>
@@ -2271,28 +2271,28 @@
         <v>445.3</v>
       </c>
       <c r="M12">
-        <v>12.076024</v>
+        <v>13.2836264</v>
       </c>
       <c r="N12">
-        <v>433.223976</v>
+        <v>432.0163736</v>
       </c>
       <c r="O12">
-        <v>108.305994</v>
+        <v>108.0040934</v>
       </c>
       <c r="P12">
-        <v>324.917982</v>
+        <v>324.0122802</v>
       </c>
       <c r="Q12">
-        <v>463.717982</v>
+        <v>462.8122802</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1585005394778373</v>
+        <v>0.1594746150135144</v>
       </c>
       <c r="T12">
-        <v>0.6892624699511964</v>
+        <v>0.6952197946698758</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.87471969250806</v>
+        <v>33.5224724477346</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1460821573620278</v>
+        <v>0.145741329194002</v>
       </c>
       <c r="C13">
-        <v>2259.149917764978</v>
+        <v>2242.370779542814</v>
       </c>
       <c r="D13">
-        <v>2411.537917764978</v>
+        <v>2418.766779542815</v>
       </c>
       <c r="E13">
-        <v>117.188</v>
+        <v>141.196</v>
       </c>
       <c r="F13">
-        <v>264.088</v>
+        <v>288.096</v>
       </c>
       <c r="G13">
         <v>111.7</v>
@@ -2353,28 +2353,28 @@
         <v>445.3</v>
       </c>
       <c r="M13">
-        <v>13.2836264</v>
+        <v>14.4912288</v>
       </c>
       <c r="N13">
-        <v>432.0163736</v>
+        <v>430.8087712</v>
       </c>
       <c r="O13">
-        <v>108.0040934</v>
+        <v>107.7021928</v>
       </c>
       <c r="P13">
-        <v>324.0122802</v>
+        <v>323.1065784</v>
       </c>
       <c r="Q13">
-        <v>462.8122802</v>
+        <v>461.9065784</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1594746150135144</v>
+        <v>0.1604708286295477</v>
       </c>
       <c r="T13">
-        <v>0.6952197946698758</v>
+        <v>0.7013125131321615</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>33.5224724477346</v>
+        <v>30.72893307709005</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.145741329194002</v>
+        <v>0.1454005010259762</v>
       </c>
       <c r="C14">
-        <v>2242.370779542814</v>
+        <v>2225.635110310191</v>
       </c>
       <c r="D14">
-        <v>2418.766779542815</v>
+        <v>2426.039110310191</v>
       </c>
       <c r="E14">
-        <v>141.196</v>
+        <v>165.204</v>
       </c>
       <c r="F14">
-        <v>288.096</v>
+        <v>312.104</v>
       </c>
       <c r="G14">
         <v>111.7</v>
@@ -2435,28 +2435,28 @@
         <v>445.3</v>
       </c>
       <c r="M14">
-        <v>14.4912288</v>
+        <v>15.6988312</v>
       </c>
       <c r="N14">
-        <v>430.8087712</v>
+        <v>429.6011688</v>
       </c>
       <c r="O14">
-        <v>107.7021928</v>
+        <v>107.4002922</v>
       </c>
       <c r="P14">
-        <v>323.1065784</v>
+        <v>322.2008766</v>
       </c>
       <c r="Q14">
-        <v>461.9065784</v>
+        <v>461.0008766</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1604708286295477</v>
+        <v>0.1614899437080186</v>
       </c>
       <c r="T14">
-        <v>0.7013125131321615</v>
+        <v>0.707545294087833</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.72893307709005</v>
+        <v>28.36516899423697</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1454005010259762</v>
+        <v>0.1450596728579505</v>
       </c>
       <c r="C15">
-        <v>2225.635110310191</v>
+        <v>2208.943303334697</v>
       </c>
       <c r="D15">
-        <v>2426.039110310191</v>
+        <v>2433.355303334698</v>
       </c>
       <c r="E15">
-        <v>165.204</v>
+        <v>189.2120000000001</v>
       </c>
       <c r="F15">
-        <v>312.104</v>
+        <v>336.1120000000001</v>
       </c>
       <c r="G15">
         <v>111.7</v>
@@ -2517,28 +2517,28 @@
         <v>445.3</v>
       </c>
       <c r="M15">
-        <v>15.6988312</v>
+        <v>16.9064336</v>
       </c>
       <c r="N15">
-        <v>429.6011688</v>
+        <v>428.3935664</v>
       </c>
       <c r="O15">
-        <v>107.4002922</v>
+        <v>107.0983916</v>
       </c>
       <c r="P15">
-        <v>322.2008766</v>
+        <v>321.2951748</v>
       </c>
       <c r="Q15">
-        <v>461.0008766</v>
+        <v>460.0951748</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1614899437080186</v>
+        <v>0.1625327591371517</v>
       </c>
       <c r="T15">
-        <v>0.707545294087833</v>
+        <v>0.7139230234378225</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>28.36516899423697</v>
+        <v>26.33908549464861</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1450596728579505</v>
+        <v>0.1447188446899247</v>
       </c>
       <c r="C16">
-        <v>2208.943303334697</v>
+        <v>2192.295756642173</v>
       </c>
       <c r="D16">
-        <v>2433.355303334698</v>
+        <v>2440.715756642173</v>
       </c>
       <c r="E16">
-        <v>189.2120000000001</v>
+        <v>213.2200000000001</v>
       </c>
       <c r="F16">
-        <v>336.1120000000001</v>
+        <v>360.1200000000001</v>
       </c>
       <c r="G16">
         <v>111.7</v>
@@ -2599,28 +2599,28 @@
         <v>445.3</v>
       </c>
       <c r="M16">
-        <v>16.9064336</v>
+        <v>18.114036</v>
       </c>
       <c r="N16">
-        <v>428.3935664</v>
+        <v>427.185964</v>
       </c>
       <c r="O16">
-        <v>107.0983916</v>
+        <v>106.796491</v>
       </c>
       <c r="P16">
-        <v>321.2951748</v>
+        <v>320.389473</v>
       </c>
       <c r="Q16">
-        <v>460.0951748</v>
+        <v>459.189473</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1625327591371517</v>
+        <v>0.1636001113999114</v>
       </c>
       <c r="T16">
-        <v>0.7139230234378225</v>
+        <v>0.7204508170078118</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>26.33908549464861</v>
+        <v>24.58314646167204</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1447188446899247</v>
+        <v>0.1443780165218989</v>
       </c>
       <c r="C17">
-        <v>2192.295756642173</v>
+        <v>2175.692873088889</v>
       </c>
       <c r="D17">
-        <v>2440.715756642173</v>
+        <v>2448.120873088889</v>
       </c>
       <c r="E17">
-        <v>213.22</v>
+        <v>237.228</v>
       </c>
       <c r="F17">
-        <v>360.12</v>
+        <v>384.128</v>
       </c>
       <c r="G17">
         <v>111.7</v>
@@ -2681,28 +2681,28 @@
         <v>445.3</v>
       </c>
       <c r="M17">
-        <v>18.114036</v>
+        <v>19.3216384</v>
       </c>
       <c r="N17">
-        <v>427.185964</v>
+        <v>425.9783616</v>
       </c>
       <c r="O17">
-        <v>106.796491</v>
+        <v>106.4945904</v>
       </c>
       <c r="P17">
-        <v>320.389473</v>
+        <v>319.4837712</v>
       </c>
       <c r="Q17">
-        <v>459.189473</v>
+        <v>458.2837712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1636001113999114</v>
+        <v>0.1646928768117844</v>
       </c>
       <c r="T17">
-        <v>0.7204508170078118</v>
+        <v>0.7271340342342293</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.58314646167204</v>
+        <v>23.04669980781754</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1443780165218989</v>
+        <v>0.1440371883538731</v>
       </c>
       <c r="C18">
-        <v>2175.692873088889</v>
+        <v>2159.135060435049</v>
       </c>
       <c r="D18">
-        <v>2448.120873088889</v>
+        <v>2455.571060435049</v>
       </c>
       <c r="E18">
-        <v>237.228</v>
+        <v>261.2360000000001</v>
       </c>
       <c r="F18">
-        <v>384.128</v>
+        <v>408.1360000000001</v>
       </c>
       <c r="G18">
         <v>111.7</v>
@@ -2763,28 +2763,28 @@
         <v>445.3</v>
       </c>
       <c r="M18">
-        <v>19.3216384</v>
+        <v>20.5292408</v>
       </c>
       <c r="N18">
-        <v>425.9783616</v>
+        <v>424.7707592</v>
       </c>
       <c r="O18">
-        <v>106.4945904</v>
+        <v>106.1926898</v>
       </c>
       <c r="P18">
-        <v>319.4837712</v>
+        <v>318.5780694</v>
       </c>
       <c r="Q18">
-        <v>458.2837712</v>
+        <v>457.3780694</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1646928768117844</v>
+        <v>0.1658119739203291</v>
       </c>
       <c r="T18">
-        <v>0.7271340342342293</v>
+        <v>0.7339782928395967</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.04669980781754</v>
+        <v>21.69101158382827</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1440371883538731</v>
+        <v>0.1436963601858473</v>
       </c>
       <c r="C19">
-        <v>2159.135060435049</v>
+        <v>2142.622731419634</v>
       </c>
       <c r="D19">
-        <v>2455.571060435049</v>
+        <v>2463.066731419634</v>
       </c>
       <c r="E19">
-        <v>261.2360000000001</v>
+        <v>285.244</v>
       </c>
       <c r="F19">
-        <v>408.1360000000001</v>
+        <v>432.1440000000001</v>
       </c>
       <c r="G19">
         <v>111.7</v>
@@ -2845,28 +2845,28 @@
         <v>445.3</v>
       </c>
       <c r="M19">
-        <v>20.5292408</v>
+        <v>21.7368432</v>
       </c>
       <c r="N19">
-        <v>424.7707592</v>
+        <v>423.5631568</v>
       </c>
       <c r="O19">
-        <v>106.1926898</v>
+        <v>105.8907892</v>
       </c>
       <c r="P19">
-        <v>318.5780694</v>
+        <v>317.6723676</v>
       </c>
       <c r="Q19">
-        <v>457.3780694</v>
+        <v>456.4723676</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1658119739203291</v>
+        <v>0.1669583660803016</v>
       </c>
       <c r="T19">
-        <v>0.7339782928395967</v>
+        <v>0.7409894845816802</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.69101158382827</v>
+        <v>20.4859553847267</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1436963601858473</v>
+        <v>0.1433555320178216</v>
       </c>
       <c r="C20">
-        <v>2142.622731419634</v>
+        <v>2126.156303836626</v>
       </c>
       <c r="D20">
-        <v>2463.066731419634</v>
+        <v>2470.608303836626</v>
       </c>
       <c r="E20">
-        <v>285.244</v>
+        <v>309.2520000000001</v>
       </c>
       <c r="F20">
-        <v>432.144</v>
+        <v>456.152</v>
       </c>
       <c r="G20">
         <v>111.7</v>
@@ -2927,28 +2927,28 @@
         <v>445.3</v>
       </c>
       <c r="M20">
-        <v>21.7368432</v>
+        <v>22.9444456</v>
       </c>
       <c r="N20">
-        <v>423.5631568</v>
+        <v>422.3555544</v>
       </c>
       <c r="O20">
-        <v>105.8907892</v>
+        <v>105.5888886</v>
       </c>
       <c r="P20">
-        <v>317.6723676</v>
+        <v>316.7666658</v>
       </c>
       <c r="Q20">
-        <v>456.4723676</v>
+        <v>455.5666658</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1669583660803016</v>
+        <v>0.1681330642195328</v>
       </c>
       <c r="T20">
-        <v>0.7409894845816802</v>
+        <v>0.7481737921692476</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.4859553847267</v>
+        <v>19.40774720658319</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1433555320178216</v>
+        <v>0.1430147038497958</v>
       </c>
       <c r="C21">
-        <v>2126.156303836626</v>
+        <v>2109.736200612637</v>
       </c>
       <c r="D21">
-        <v>2470.608303836626</v>
+        <v>2478.196200612637</v>
       </c>
       <c r="E21">
-        <v>309.2520000000001</v>
+        <v>333.2600000000001</v>
       </c>
       <c r="F21">
-        <v>456.152</v>
+        <v>480.1600000000001</v>
       </c>
       <c r="G21">
         <v>111.7</v>
@@ -3009,28 +3009,28 @@
         <v>445.3</v>
       </c>
       <c r="M21">
-        <v>22.9444456</v>
+        <v>24.152048</v>
       </c>
       <c r="N21">
-        <v>422.3555544</v>
+        <v>421.147952</v>
       </c>
       <c r="O21">
-        <v>105.5888886</v>
+        <v>105.286988</v>
       </c>
       <c r="P21">
-        <v>316.7666658</v>
+        <v>315.860964</v>
       </c>
       <c r="Q21">
-        <v>455.5666658</v>
+        <v>454.660964</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1681330642195328</v>
+        <v>0.1693371298122447</v>
       </c>
       <c r="T21">
-        <v>0.7481737921692476</v>
+        <v>0.7555377074465038</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.40774720658319</v>
+        <v>18.43735984625403</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1430147038497958</v>
+        <v>0.14267387568177</v>
       </c>
       <c r="C22">
-        <v>2109.736200612637</v>
+        <v>2093.362849885962</v>
       </c>
       <c r="D22">
-        <v>2478.196200612637</v>
+        <v>2485.830849885962</v>
       </c>
       <c r="E22">
-        <v>333.2600000000001</v>
+        <v>357.268</v>
       </c>
       <c r="F22">
-        <v>480.1600000000001</v>
+        <v>504.1680000000001</v>
       </c>
       <c r="G22">
         <v>111.7</v>
@@ -3091,28 +3091,28 @@
         <v>445.3</v>
       </c>
       <c r="M22">
-        <v>24.152048</v>
+        <v>25.3596504</v>
       </c>
       <c r="N22">
-        <v>421.147952</v>
+        <v>419.9403496</v>
       </c>
       <c r="O22">
-        <v>105.286988</v>
+        <v>104.9850874</v>
       </c>
       <c r="P22">
-        <v>315.860964</v>
+        <v>314.9552622</v>
       </c>
       <c r="Q22">
-        <v>454.660964</v>
+        <v>453.7552622</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1693371298122447</v>
+        <v>0.1705716780781899</v>
       </c>
       <c r="T22">
-        <v>0.7555377074465038</v>
+        <v>0.7630880509586275</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.43735984625403</v>
+        <v>17.55939032976574</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.14267387568177</v>
+        <v>0.1423330475137442</v>
       </c>
       <c r="C23">
-        <v>2093.362849885962</v>
+        <v>2077.036685087114</v>
       </c>
       <c r="D23">
-        <v>2485.830849885962</v>
+        <v>2493.512685087114</v>
       </c>
       <c r="E23">
-        <v>357.268</v>
+        <v>381.2760000000001</v>
       </c>
       <c r="F23">
-        <v>504.168</v>
+        <v>528.176</v>
       </c>
       <c r="G23">
         <v>111.7</v>
@@ -3173,28 +3173,28 @@
         <v>445.3</v>
       </c>
       <c r="M23">
-        <v>25.3596504</v>
+        <v>26.5672528</v>
       </c>
       <c r="N23">
-        <v>419.9403496</v>
+        <v>418.7327472</v>
       </c>
       <c r="O23">
-        <v>104.9850874</v>
+        <v>104.6831868</v>
       </c>
       <c r="P23">
-        <v>314.9552622</v>
+        <v>314.0495604</v>
       </c>
       <c r="Q23">
-        <v>453.7552622</v>
+        <v>452.8495604</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1705716780781899</v>
+        <v>0.1718378814278772</v>
       </c>
       <c r="T23">
-        <v>0.7630880509586275</v>
+        <v>0.770831993022344</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.55939032976574</v>
+        <v>16.7612362238673</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1423330475137442</v>
+        <v>0.1419922193457185</v>
       </c>
       <c r="C24">
-        <v>2077.036685087114</v>
+        <v>2060.758145020844</v>
       </c>
       <c r="D24">
-        <v>2493.512685087114</v>
+        <v>2501.242145020844</v>
       </c>
       <c r="E24">
-        <v>381.2760000000001</v>
+        <v>405.2840000000001</v>
       </c>
       <c r="F24">
-        <v>528.176</v>
+        <v>552.1840000000001</v>
       </c>
       <c r="G24">
         <v>111.7</v>
@@ -3255,28 +3255,28 @@
         <v>445.3</v>
       </c>
       <c r="M24">
-        <v>26.5672528</v>
+        <v>27.7748552</v>
       </c>
       <c r="N24">
-        <v>418.7327472</v>
+        <v>417.5251448</v>
       </c>
       <c r="O24">
-        <v>104.6831868</v>
+        <v>104.3812862</v>
       </c>
       <c r="P24">
-        <v>314.0495604</v>
+        <v>313.1438586</v>
       </c>
       <c r="Q24">
-        <v>452.8495604</v>
+        <v>451.9438586000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1718378814278772</v>
+        <v>0.1731369731762577</v>
       </c>
       <c r="T24">
-        <v>0.770831993022344</v>
+        <v>0.7787770764383649</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.7612362238673</v>
+        <v>16.03248682282959</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1419922193457185</v>
+        <v>0.1416513911776927</v>
       </c>
       <c r="C25">
-        <v>2060.758145020844</v>
+        <v>2044.5276739497</v>
       </c>
       <c r="D25">
-        <v>2501.242145020844</v>
+        <v>2509.019673949701</v>
       </c>
       <c r="E25">
-        <v>405.2840000000001</v>
+        <v>429.2920000000001</v>
       </c>
       <c r="F25">
-        <v>552.1840000000001</v>
+        <v>576.1920000000001</v>
       </c>
       <c r="G25">
         <v>111.7</v>
@@ -3337,28 +3337,28 @@
         <v>445.3</v>
       </c>
       <c r="M25">
-        <v>27.7748552</v>
+        <v>28.9824576</v>
       </c>
       <c r="N25">
-        <v>417.5251448</v>
+        <v>416.3175424</v>
       </c>
       <c r="O25">
-        <v>104.3812862</v>
+        <v>104.0793856</v>
       </c>
       <c r="P25">
-        <v>313.1438586</v>
+        <v>312.2381568</v>
       </c>
       <c r="Q25">
-        <v>451.9438586000001</v>
+        <v>451.0381568</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1731369731762577</v>
+        <v>0.1744702515495956</v>
       </c>
       <c r="T25">
-        <v>0.7787770764383649</v>
+        <v>0.7869312409969127</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.03248682282959</v>
+        <v>15.36446653854502</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1416513911776927</v>
+        <v>0.1413105630096669</v>
       </c>
       <c r="C26">
-        <v>2044.5276739497</v>
+        <v>2028.345721679144</v>
       </c>
       <c r="D26">
-        <v>2509.019673949701</v>
+        <v>2516.845721679144</v>
       </c>
       <c r="E26">
-        <v>429.292</v>
+        <v>453.3000000000001</v>
       </c>
       <c r="F26">
-        <v>576.192</v>
+        <v>600.2</v>
       </c>
       <c r="G26">
         <v>111.7</v>
@@ -3419,28 +3419,28 @@
         <v>445.3</v>
       </c>
       <c r="M26">
-        <v>28.9824576</v>
+        <v>30.19006</v>
       </c>
       <c r="N26">
-        <v>416.3175424</v>
+        <v>415.10994</v>
       </c>
       <c r="O26">
-        <v>104.0793856</v>
+        <v>103.777485</v>
       </c>
       <c r="P26">
-        <v>312.2381568</v>
+        <v>311.332455</v>
       </c>
       <c r="Q26">
-        <v>451.0381568</v>
+        <v>450.132455</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1744702515495956</v>
+        <v>0.1758390840128892</v>
       </c>
       <c r="T26">
-        <v>0.7869312409969127</v>
+        <v>0.7953028499436883</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.36446653854503</v>
+        <v>14.74988787700323</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1413105630096669</v>
+        <v>0.1409697348416411</v>
       </c>
       <c r="C27">
-        <v>2028.345721679144</v>
+        <v>2012.212743644265</v>
       </c>
       <c r="D27">
-        <v>2516.845721679144</v>
+        <v>2524.720743644265</v>
       </c>
       <c r="E27">
-        <v>453.3000000000001</v>
+        <v>477.3080000000001</v>
       </c>
       <c r="F27">
-        <v>600.2</v>
+        <v>624.2080000000001</v>
       </c>
       <c r="G27">
         <v>111.7</v>
@@ -3501,28 +3501,28 @@
         <v>445.3</v>
       </c>
       <c r="M27">
-        <v>30.19006</v>
+        <v>31.3976624</v>
       </c>
       <c r="N27">
-        <v>415.10994</v>
+        <v>413.9023376</v>
       </c>
       <c r="O27">
-        <v>103.777485</v>
+        <v>103.4755844</v>
       </c>
       <c r="P27">
-        <v>311.332455</v>
+        <v>310.4267532</v>
       </c>
       <c r="Q27">
-        <v>450.132455</v>
+        <v>449.2267532</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1758390840128892</v>
+        <v>0.1772449119481637</v>
       </c>
       <c r="T27">
-        <v>0.7953028499436883</v>
+        <v>0.8039007185917282</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.74988787700323</v>
+        <v>14.18258449711849</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1409697348416411</v>
+        <v>0.1406289066736154</v>
       </c>
       <c r="C28">
-        <v>2012.212743644265</v>
+        <v>1996.129200998137</v>
       </c>
       <c r="D28">
-        <v>2524.720743644265</v>
+        <v>2532.645200998137</v>
       </c>
       <c r="E28">
-        <v>477.3080000000001</v>
+        <v>501.3160000000001</v>
       </c>
       <c r="F28">
-        <v>624.2080000000001</v>
+        <v>648.2160000000001</v>
       </c>
       <c r="G28">
         <v>111.7</v>
@@ -3583,28 +3583,28 @@
         <v>445.3</v>
       </c>
       <c r="M28">
-        <v>31.3976624</v>
+        <v>32.60526480000001</v>
       </c>
       <c r="N28">
-        <v>413.9023376</v>
+        <v>412.6947352</v>
       </c>
       <c r="O28">
-        <v>103.4755844</v>
+        <v>103.1736838</v>
       </c>
       <c r="P28">
-        <v>310.4267532</v>
+        <v>309.5210514</v>
       </c>
       <c r="Q28">
-        <v>449.2267532</v>
+        <v>448.3210514</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1772449119481637</v>
+        <v>0.1786892557172813</v>
       </c>
       <c r="T28">
-        <v>0.8039007185917282</v>
+        <v>0.8127341452849199</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.18258449711849</v>
+        <v>13.6573035898178</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1406289066736154</v>
+        <v>0.1402880785055896</v>
       </c>
       <c r="C29">
-        <v>1996.129200998137</v>
+        <v>1980.095560701829</v>
       </c>
       <c r="D29">
-        <v>2532.645200998137</v>
+        <v>2540.619560701829</v>
       </c>
       <c r="E29">
-        <v>501.3160000000001</v>
+        <v>525.3240000000002</v>
       </c>
       <c r="F29">
-        <v>648.2160000000001</v>
+        <v>672.2240000000002</v>
       </c>
       <c r="G29">
         <v>111.7</v>
@@ -3665,28 +3665,28 @@
         <v>445.3</v>
       </c>
       <c r="M29">
-        <v>32.60526480000001</v>
+        <v>33.81286720000001</v>
       </c>
       <c r="N29">
-        <v>412.6947352</v>
+        <v>411.4871328</v>
       </c>
       <c r="O29">
-        <v>103.1736838</v>
+        <v>102.8717832</v>
       </c>
       <c r="P29">
-        <v>309.5210514</v>
+        <v>308.6153496</v>
       </c>
       <c r="Q29">
-        <v>448.3210514</v>
+        <v>447.4153496</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1786892557172813</v>
+        <v>0.1801737201466522</v>
       </c>
       <c r="T29">
-        <v>0.8127341452849199</v>
+        <v>0.8218129449418113</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.6573035898178</v>
+        <v>13.16954274732431</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1402880785055896</v>
+        <v>0.1402735003375638</v>
       </c>
       <c r="C30">
-        <v>1980.095560701829</v>
+        <v>1956.429766268329</v>
       </c>
       <c r="D30">
-        <v>2540.619560701829</v>
+        <v>2540.961766268329</v>
       </c>
       <c r="E30">
-        <v>525.3240000000002</v>
+        <v>549.3320000000001</v>
       </c>
       <c r="F30">
-        <v>672.2240000000002</v>
+        <v>696.2320000000001</v>
       </c>
       <c r="G30">
         <v>111.7</v>
@@ -3747,45 +3747,45 @@
         <v>445.3</v>
       </c>
       <c r="M30">
-        <v>33.81286720000001</v>
+        <v>36.0648176</v>
       </c>
       <c r="N30">
-        <v>411.4871328</v>
+        <v>409.2351824</v>
       </c>
       <c r="O30">
-        <v>102.8717832</v>
+        <v>102.3087956</v>
       </c>
       <c r="P30">
-        <v>308.6153496</v>
+        <v>306.9263868</v>
       </c>
       <c r="Q30">
-        <v>447.4153496</v>
+        <v>445.7263868</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1801737201466522</v>
+        <v>0.1817000004754419</v>
       </c>
       <c r="T30">
-        <v>0.8218129449418113</v>
+        <v>0.831147485434108</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>13.16954274732431</v>
+        <v>12.34721342386603</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1402735003375638</v>
+        <v>0.139943922169538</v>
       </c>
       <c r="C31">
-        <v>1956.42976626833</v>
+        <v>1940.182906638321</v>
       </c>
       <c r="D31">
-        <v>2540.96176626833</v>
+        <v>2548.722906638322</v>
       </c>
       <c r="E31">
-        <v>549.332</v>
+        <v>573.34</v>
       </c>
       <c r="F31">
-        <v>696.232</v>
+        <v>720.24</v>
       </c>
       <c r="G31">
         <v>111.7</v>
@@ -3829,28 +3829,28 @@
         <v>445.3</v>
       </c>
       <c r="M31">
-        <v>36.0648176</v>
+        <v>37.308432</v>
       </c>
       <c r="N31">
-        <v>409.2351824</v>
+        <v>407.991568</v>
       </c>
       <c r="O31">
-        <v>102.3087956</v>
+        <v>101.997892</v>
       </c>
       <c r="P31">
-        <v>306.9263868</v>
+        <v>305.9936760000001</v>
       </c>
       <c r="Q31">
-        <v>445.7263868</v>
+        <v>444.7936760000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1817000004754419</v>
+        <v>0.1832698888136257</v>
       </c>
       <c r="T31">
-        <v>0.831147485434108</v>
+        <v>0.8407487270833276</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.34721342386603</v>
+        <v>11.9356396430705</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.139943922169538</v>
+        <v>0.1396143440015122</v>
       </c>
       <c r="C32">
-        <v>1940.182906638321</v>
+        <v>1923.983603683633</v>
       </c>
       <c r="D32">
-        <v>2548.722906638322</v>
+        <v>2556.531603683633</v>
       </c>
       <c r="E32">
-        <v>573.34</v>
+        <v>597.3480000000001</v>
       </c>
       <c r="F32">
-        <v>720.24</v>
+        <v>744.248</v>
       </c>
       <c r="G32">
         <v>111.7</v>
@@ -3911,28 +3911,28 @@
         <v>445.3</v>
       </c>
       <c r="M32">
-        <v>37.308432</v>
+        <v>38.5520464</v>
       </c>
       <c r="N32">
-        <v>407.991568</v>
+        <v>406.7479536</v>
       </c>
       <c r="O32">
-        <v>101.997892</v>
+        <v>101.6869884</v>
       </c>
       <c r="P32">
-        <v>305.9936760000001</v>
+        <v>305.0609652</v>
       </c>
       <c r="Q32">
-        <v>444.7936760000001</v>
+        <v>443.8609652</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1832698888136257</v>
+        <v>0.1848852811616119</v>
       </c>
       <c r="T32">
-        <v>0.8407487270833276</v>
+        <v>0.8506282655919448</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.9356396430705</v>
+        <v>11.55061900942306</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1396143440015122</v>
+        <v>0.1392847658334865</v>
       </c>
       <c r="C33">
-        <v>1923.983603683633</v>
+        <v>1907.832295855514</v>
       </c>
       <c r="D33">
-        <v>2556.531603683633</v>
+        <v>2564.388295855515</v>
       </c>
       <c r="E33">
-        <v>597.3480000000001</v>
+        <v>621.3560000000001</v>
       </c>
       <c r="F33">
-        <v>744.248</v>
+        <v>768.2560000000001</v>
       </c>
       <c r="G33">
         <v>111.7</v>
@@ -3993,28 +3993,28 @@
         <v>445.3</v>
       </c>
       <c r="M33">
-        <v>38.5520464</v>
+        <v>39.7956608</v>
       </c>
       <c r="N33">
-        <v>406.7479536</v>
+        <v>405.5043392</v>
       </c>
       <c r="O33">
-        <v>101.6869884</v>
+        <v>101.3760848</v>
       </c>
       <c r="P33">
-        <v>305.0609652</v>
+        <v>304.1282544</v>
       </c>
       <c r="Q33">
-        <v>443.8609652</v>
+        <v>442.9282544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1848852811616119</v>
+        <v>0.1865481850492448</v>
       </c>
       <c r="T33">
-        <v>0.8506282655919448</v>
+        <v>0.8607983787625804</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.55061900942306</v>
+        <v>11.18966216537859</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1392847658334865</v>
+        <v>0.1389551876654607</v>
       </c>
       <c r="C34">
-        <v>1907.832295855514</v>
+        <v>1891.729427011594</v>
       </c>
       <c r="D34">
-        <v>2564.388295855515</v>
+        <v>2572.293427011595</v>
       </c>
       <c r="E34">
-        <v>621.3560000000001</v>
+        <v>645.3640000000001</v>
       </c>
       <c r="F34">
-        <v>768.2560000000001</v>
+        <v>792.2640000000001</v>
       </c>
       <c r="G34">
         <v>111.7</v>
@@ -4075,28 +4075,28 @@
         <v>445.3</v>
       </c>
       <c r="M34">
-        <v>39.7956608</v>
+        <v>41.03927520000001</v>
       </c>
       <c r="N34">
-        <v>405.5043392</v>
+        <v>404.2607248</v>
       </c>
       <c r="O34">
-        <v>101.3760848</v>
+        <v>101.0651812</v>
       </c>
       <c r="P34">
-        <v>304.1282544</v>
+        <v>303.1955436</v>
       </c>
       <c r="Q34">
-        <v>442.9282544</v>
+        <v>441.9955436</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1865481850492448</v>
+        <v>0.1882607278588965</v>
       </c>
       <c r="T34">
-        <v>0.8607983787625804</v>
+        <v>0.8712720774009959</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.18966216537859</v>
+        <v>10.85058149370045</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1389551876654607</v>
+        <v>0.1386256094974349</v>
       </c>
       <c r="C35">
-        <v>1891.729427011594</v>
+        <v>1875.675446499471</v>
       </c>
       <c r="D35">
-        <v>2572.293427011595</v>
+        <v>2580.247446499472</v>
       </c>
       <c r="E35">
-        <v>645.3640000000001</v>
+        <v>669.3720000000002</v>
       </c>
       <c r="F35">
-        <v>792.2640000000001</v>
+        <v>816.2720000000002</v>
       </c>
       <c r="G35">
         <v>111.7</v>
@@ -4157,28 +4157,28 @@
         <v>445.3</v>
       </c>
       <c r="M35">
-        <v>41.03927520000001</v>
+        <v>42.2828896</v>
       </c>
       <c r="N35">
-        <v>404.2607248</v>
+        <v>403.0171104</v>
       </c>
       <c r="O35">
-        <v>101.0651812</v>
+        <v>100.7542776</v>
       </c>
       <c r="P35">
-        <v>303.1955436</v>
+        <v>302.2628328</v>
       </c>
       <c r="Q35">
-        <v>441.9955436</v>
+        <v>441.0628328</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1882607278588965</v>
+        <v>0.1900251659052044</v>
       </c>
       <c r="T35">
-        <v>0.8712720774009959</v>
+        <v>0.8820631608466362</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.85058149370045</v>
+        <v>10.53144674388573</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1386256094974349</v>
+        <v>0.1382960313294091</v>
       </c>
       <c r="C36">
-        <v>1875.675446499471</v>
+        <v>1859.670809241856</v>
       </c>
       <c r="D36">
-        <v>2580.247446499472</v>
+        <v>2588.250809241856</v>
       </c>
       <c r="E36">
-        <v>669.3720000000002</v>
+        <v>693.3800000000002</v>
       </c>
       <c r="F36">
-        <v>816.2720000000002</v>
+        <v>840.2800000000002</v>
       </c>
       <c r="G36">
         <v>111.7</v>
@@ -4239,28 +4239,28 @@
         <v>445.3</v>
       </c>
       <c r="M36">
-        <v>42.2828896</v>
+        <v>43.52650400000001</v>
       </c>
       <c r="N36">
-        <v>403.0171104</v>
+        <v>401.773496</v>
       </c>
       <c r="O36">
-        <v>100.7542776</v>
+        <v>100.443374</v>
       </c>
       <c r="P36">
-        <v>302.2628328</v>
+        <v>301.330122</v>
       </c>
       <c r="Q36">
-        <v>441.0628328</v>
+        <v>440.130122</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1900251659052044</v>
+        <v>0.1918438943529371</v>
       </c>
       <c r="T36">
-        <v>0.8820631608466362</v>
+        <v>0.8931862776290654</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.53144674388573</v>
+        <v>10.230548265489</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1382960313294091</v>
+        <v>0.1379664531613833</v>
       </c>
       <c r="C37">
-        <v>1859.670809241856</v>
+        <v>1843.715975823301</v>
       </c>
       <c r="D37">
-        <v>2588.250809241856</v>
+        <v>2596.303975823301</v>
       </c>
       <c r="E37">
-        <v>693.3800000000002</v>
+        <v>717.3880000000001</v>
       </c>
       <c r="F37">
-        <v>840.2800000000002</v>
+        <v>864.2880000000001</v>
       </c>
       <c r="G37">
         <v>111.7</v>
@@ -4321,28 +4321,28 @@
         <v>445.3</v>
       </c>
       <c r="M37">
-        <v>43.52650400000001</v>
+        <v>44.77011840000001</v>
       </c>
       <c r="N37">
-        <v>401.773496</v>
+        <v>400.5298816</v>
       </c>
       <c r="O37">
-        <v>100.443374</v>
+        <v>100.1324704</v>
       </c>
       <c r="P37">
-        <v>301.330122</v>
+        <v>300.3974112</v>
       </c>
       <c r="Q37">
-        <v>440.130122</v>
+        <v>439.1974112</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1918438943529371</v>
+        <v>0.1937194580646615</v>
       </c>
       <c r="T37">
-        <v>0.8931862776290654</v>
+        <v>0.9046569918109454</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.230548265489</v>
+        <v>9.946366369225414</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1379664531613833</v>
+        <v>0.1381086249933575</v>
       </c>
       <c r="C38">
-        <v>1843.7159758233</v>
+        <v>1816.227901894078</v>
       </c>
       <c r="D38">
-        <v>2596.3039758233</v>
+        <v>2592.823901894078</v>
       </c>
       <c r="E38">
-        <v>717.388</v>
+        <v>741.3960000000001</v>
       </c>
       <c r="F38">
-        <v>864.288</v>
+        <v>888.296</v>
       </c>
       <c r="G38">
         <v>111.7</v>
@@ -4403,45 +4403,45 @@
         <v>445.3</v>
       </c>
       <c r="M38">
-        <v>44.7701184</v>
+        <v>47.523836</v>
       </c>
       <c r="N38">
-        <v>400.5298816</v>
+        <v>397.776164</v>
       </c>
       <c r="O38">
-        <v>100.1324704</v>
+        <v>99.444041</v>
       </c>
       <c r="P38">
-        <v>300.3974112</v>
+        <v>298.332123</v>
       </c>
       <c r="Q38">
-        <v>439.1974112</v>
+        <v>437.132123</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1937194580646615</v>
+        <v>0.1956545634815199</v>
       </c>
       <c r="T38">
-        <v>0.9046569918109454</v>
+        <v>0.9164918556493932</v>
       </c>
       <c r="U38">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>9.946366369225416</v>
+        <v>9.370034859980578</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1381086249933575</v>
+        <v>0.1377917968253318</v>
       </c>
       <c r="C39">
-        <v>1816.227901894078</v>
+        <v>1799.988012174327</v>
       </c>
       <c r="D39">
-        <v>2592.823901894078</v>
+        <v>2600.592012174327</v>
       </c>
       <c r="E39">
-        <v>741.3960000000001</v>
+        <v>765.4040000000001</v>
       </c>
       <c r="F39">
-        <v>888.296</v>
+        <v>912.3040000000001</v>
       </c>
       <c r="G39">
         <v>111.7</v>
@@ -4485,28 +4485,28 @@
         <v>445.3</v>
       </c>
       <c r="M39">
-        <v>47.523836</v>
+        <v>48.808264</v>
       </c>
       <c r="N39">
-        <v>397.776164</v>
+        <v>396.491736</v>
       </c>
       <c r="O39">
-        <v>99.444041</v>
+        <v>99.122934</v>
       </c>
       <c r="P39">
-        <v>298.332123</v>
+        <v>297.368802</v>
       </c>
       <c r="Q39">
-        <v>437.132123</v>
+        <v>436.168802</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1956545634815199</v>
+        <v>0.1976520916537609</v>
       </c>
       <c r="T39">
-        <v>0.9164918556493932</v>
+        <v>0.9287084892890812</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.370034859980578</v>
+        <v>9.123454995244249</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1377917968253318</v>
+        <v>0.137474968657306</v>
       </c>
       <c r="C40">
-        <v>1799.988012174327</v>
+        <v>1783.794808903295</v>
       </c>
       <c r="D40">
-        <v>2600.592012174327</v>
+        <v>2608.406808903296</v>
       </c>
       <c r="E40">
-        <v>765.4040000000001</v>
+        <v>789.4120000000001</v>
       </c>
       <c r="F40">
-        <v>912.3040000000001</v>
+        <v>936.3120000000001</v>
       </c>
       <c r="G40">
         <v>111.7</v>
@@ -4567,28 +4567,28 @@
         <v>445.3</v>
       </c>
       <c r="M40">
-        <v>48.808264</v>
+        <v>50.09269200000001</v>
       </c>
       <c r="N40">
-        <v>396.491736</v>
+        <v>395.207308</v>
       </c>
       <c r="O40">
-        <v>99.122934</v>
+        <v>98.801827</v>
       </c>
       <c r="P40">
-        <v>297.368802</v>
+        <v>296.405481</v>
       </c>
       <c r="Q40">
-        <v>436.168802</v>
+        <v>435.205481</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1976520916537609</v>
+        <v>0.1997151125529607</v>
       </c>
       <c r="T40">
-        <v>0.9287084892890812</v>
+        <v>0.9413256682940049</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.123454995244249</v>
+        <v>8.889520251776446</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.137474968657306</v>
+        <v>0.1371581404892802</v>
       </c>
       <c r="C41">
-        <v>1783.794808903295</v>
+        <v>1767.648714228832</v>
       </c>
       <c r="D41">
-        <v>2608.406808903296</v>
+        <v>2616.268714228832</v>
       </c>
       <c r="E41">
-        <v>789.4120000000001</v>
+        <v>813.4200000000002</v>
       </c>
       <c r="F41">
-        <v>936.3120000000001</v>
+        <v>960.3200000000002</v>
       </c>
       <c r="G41">
         <v>111.7</v>
@@ -4649,28 +4649,28 @@
         <v>445.3</v>
       </c>
       <c r="M41">
-        <v>50.09269200000001</v>
+        <v>51.37712000000001</v>
       </c>
       <c r="N41">
-        <v>395.207308</v>
+        <v>393.92288</v>
       </c>
       <c r="O41">
-        <v>98.801827</v>
+        <v>98.48072000000001</v>
       </c>
       <c r="P41">
-        <v>296.405481</v>
+        <v>295.44216</v>
       </c>
       <c r="Q41">
-        <v>435.205481</v>
+        <v>434.24216</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1997151125529607</v>
+        <v>0.2018469008154671</v>
       </c>
       <c r="T41">
-        <v>0.9413256682940049</v>
+        <v>0.954363419932426</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.889520251776446</v>
+        <v>8.667282245482035</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1371581404892802</v>
+        <v>0.1368413123212545</v>
       </c>
       <c r="C42">
-        <v>1767.648714228832</v>
+        <v>1751.55015540369</v>
       </c>
       <c r="D42">
-        <v>2616.268714228832</v>
+        <v>2624.178155403691</v>
       </c>
       <c r="E42">
-        <v>813.4200000000002</v>
+        <v>837.4280000000002</v>
       </c>
       <c r="F42">
-        <v>960.3200000000002</v>
+        <v>984.3280000000002</v>
       </c>
       <c r="G42">
         <v>111.7</v>
@@ -4731,28 +4731,28 @@
         <v>445.3</v>
       </c>
       <c r="M42">
-        <v>51.37712000000001</v>
+        <v>52.66154800000001</v>
       </c>
       <c r="N42">
-        <v>393.92288</v>
+        <v>392.638452</v>
       </c>
       <c r="O42">
-        <v>98.48072000000001</v>
+        <v>98.15961300000001</v>
       </c>
       <c r="P42">
-        <v>295.44216</v>
+        <v>294.478839</v>
       </c>
       <c r="Q42">
-        <v>434.24216</v>
+        <v>433.278839</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2018469008154671</v>
+        <v>0.204050953086872</v>
       </c>
       <c r="T42">
-        <v>0.954363419932426</v>
+        <v>0.9678431292535056</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.667282245482035</v>
+        <v>8.455885117543449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1368413123212545</v>
+        <v>0.1365244841532287</v>
       </c>
       <c r="C43">
-        <v>1751.55015540369</v>
+        <v>1735.499564862939</v>
       </c>
       <c r="D43">
-        <v>2624.178155403691</v>
+        <v>2632.13556486294</v>
       </c>
       <c r="E43">
-        <v>837.4280000000002</v>
+        <v>861.4360000000001</v>
       </c>
       <c r="F43">
-        <v>984.3280000000002</v>
+        <v>1008.336</v>
       </c>
       <c r="G43">
         <v>111.7</v>
@@ -4813,28 +4813,28 @@
         <v>445.3</v>
       </c>
       <c r="M43">
-        <v>52.66154800000001</v>
+        <v>53.94597600000001</v>
       </c>
       <c r="N43">
-        <v>392.638452</v>
+        <v>391.354024</v>
       </c>
       <c r="O43">
-        <v>98.15961300000001</v>
+        <v>97.838506</v>
       </c>
       <c r="P43">
-        <v>294.478839</v>
+        <v>293.515518</v>
       </c>
       <c r="Q43">
-        <v>433.278839</v>
+        <v>432.315518</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.204050953086872</v>
+        <v>0.2063310071607391</v>
       </c>
       <c r="T43">
-        <v>0.9678431292535056</v>
+        <v>0.9817876561373807</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.455885117543449</v>
+        <v>8.254554519506698</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1365244841532287</v>
+        <v>0.1362076559852029</v>
       </c>
       <c r="C44">
-        <v>1735.499564862938</v>
+        <v>1719.49738030276</v>
       </c>
       <c r="D44">
-        <v>2632.135564862938</v>
+        <v>2640.14138030276</v>
       </c>
       <c r="E44">
-        <v>861.436</v>
+        <v>885.4440000000001</v>
       </c>
       <c r="F44">
-        <v>1008.336</v>
+        <v>1032.344</v>
       </c>
       <c r="G44">
         <v>111.7</v>
@@ -4895,28 +4895,28 @@
         <v>445.3</v>
       </c>
       <c r="M44">
-        <v>53.945976</v>
+        <v>55.230404</v>
       </c>
       <c r="N44">
-        <v>391.354024</v>
+        <v>390.069596</v>
       </c>
       <c r="O44">
-        <v>97.838506</v>
+        <v>97.517399</v>
       </c>
       <c r="P44">
-        <v>293.515518</v>
+        <v>292.552197</v>
       </c>
       <c r="Q44">
-        <v>432.315518</v>
+        <v>431.352197</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2063310071607391</v>
+        <v>0.2086910631319349</v>
       </c>
       <c r="T44">
-        <v>0.9817876561373807</v>
+        <v>0.9962214646663042</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.2545545195067</v>
+        <v>8.062588135332126</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1362076559852029</v>
+        <v>0.1358908278171771</v>
       </c>
       <c r="C45">
-        <v>1719.49738030276</v>
+        <v>1703.544044760714</v>
       </c>
       <c r="D45">
-        <v>2640.14138030276</v>
+        <v>2648.196044760714</v>
       </c>
       <c r="E45">
-        <v>885.4440000000001</v>
+        <v>909.4520000000001</v>
       </c>
       <c r="F45">
-        <v>1032.344</v>
+        <v>1056.352</v>
       </c>
       <c r="G45">
         <v>111.7</v>
@@ -4977,28 +4977,28 @@
         <v>445.3</v>
       </c>
       <c r="M45">
-        <v>55.230404</v>
+        <v>56.51483200000001</v>
       </c>
       <c r="N45">
-        <v>390.069596</v>
+        <v>388.785168</v>
       </c>
       <c r="O45">
-        <v>97.517399</v>
+        <v>97.196292</v>
       </c>
       <c r="P45">
-        <v>292.552197</v>
+        <v>291.588876</v>
       </c>
       <c r="Q45">
-        <v>431.352197</v>
+        <v>430.388876</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2086910631319349</v>
+        <v>0.2111354068163877</v>
       </c>
       <c r="T45">
-        <v>0.9962214646663042</v>
+        <v>1.011170766356975</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.062588135332126</v>
+        <v>7.879347495892759</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1358908278171771</v>
+        <v>0.1355739996491513</v>
       </c>
       <c r="C46">
-        <v>1703.544044760714</v>
+        <v>1687.640006697463</v>
       </c>
       <c r="D46">
-        <v>2648.196044760714</v>
+        <v>2656.300006697463</v>
       </c>
       <c r="E46">
-        <v>909.4520000000001</v>
+        <v>933.4600000000002</v>
       </c>
       <c r="F46">
-        <v>1056.352</v>
+        <v>1080.36</v>
       </c>
       <c r="G46">
         <v>111.7</v>
@@ -5059,28 +5059,28 @@
         <v>445.3</v>
       </c>
       <c r="M46">
-        <v>56.51483200000001</v>
+        <v>57.79926</v>
       </c>
       <c r="N46">
-        <v>388.785168</v>
+        <v>387.50074</v>
       </c>
       <c r="O46">
-        <v>97.196292</v>
+        <v>96.875185</v>
       </c>
       <c r="P46">
-        <v>291.588876</v>
+        <v>290.625555</v>
       </c>
       <c r="Q46">
-        <v>430.388876</v>
+        <v>429.425555</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2111354068163877</v>
+        <v>0.2136686357257297</v>
       </c>
       <c r="T46">
-        <v>1.011170766356975</v>
+        <v>1.026663679018216</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.879347495892759</v>
+        <v>7.70425088487292</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1355739996491513</v>
+        <v>0.1355331714811255</v>
       </c>
       <c r="C47">
-        <v>1687.640006697463</v>
+        <v>1664.679935528445</v>
       </c>
       <c r="D47">
-        <v>2656.300006697463</v>
+        <v>2657.347935528445</v>
       </c>
       <c r="E47">
-        <v>933.4600000000002</v>
+        <v>957.4680000000002</v>
       </c>
       <c r="F47">
-        <v>1080.36</v>
+        <v>1104.368</v>
       </c>
       <c r="G47">
         <v>111.7</v>
@@ -5141,45 +5141,45 @@
         <v>445.3</v>
       </c>
       <c r="M47">
-        <v>57.79926</v>
+        <v>59.96718240000001</v>
       </c>
       <c r="N47">
-        <v>387.50074</v>
+        <v>385.3328176</v>
       </c>
       <c r="O47">
-        <v>96.875185</v>
+        <v>96.3332044</v>
       </c>
       <c r="P47">
-        <v>290.625555</v>
+        <v>288.9996132</v>
       </c>
       <c r="Q47">
-        <v>429.425555</v>
+        <v>427.7996132</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2136686357257297</v>
+        <v>0.2162956879280103</v>
       </c>
       <c r="T47">
-        <v>1.026663679018216</v>
+        <v>1.042730403259502</v>
       </c>
       <c r="U47">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y47">
-        <v>7.70425088487292</v>
+        <v>7.425728242986449</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1355331714811255</v>
+        <v>0.1352223433130998</v>
       </c>
       <c r="C48">
-        <v>1664.679935528445</v>
+        <v>1648.677093219934</v>
       </c>
       <c r="D48">
-        <v>2657.347935528445</v>
+        <v>2665.353093219935</v>
       </c>
       <c r="E48">
-        <v>957.4680000000002</v>
+        <v>981.4760000000002</v>
       </c>
       <c r="F48">
-        <v>1104.368</v>
+        <v>1128.376</v>
       </c>
       <c r="G48">
         <v>111.7</v>
@@ -5223,28 +5223,28 @@
         <v>445.3</v>
       </c>
       <c r="M48">
-        <v>59.96718240000001</v>
+        <v>61.27081680000001</v>
       </c>
       <c r="N48">
-        <v>385.3328176</v>
+        <v>384.0291832</v>
       </c>
       <c r="O48">
-        <v>96.3332044</v>
+        <v>96.00729579999999</v>
       </c>
       <c r="P48">
-        <v>288.9996132</v>
+        <v>288.0218874</v>
       </c>
       <c r="Q48">
-        <v>427.7996132</v>
+        <v>426.8218874</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2162956879280103</v>
+        <v>0.2190218741756599</v>
       </c>
       <c r="T48">
-        <v>1.042730403259502</v>
+        <v>1.059403418981592</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.425728242986449</v>
+        <v>7.267734025050567</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1352223433130998</v>
+        <v>0.134911515145074</v>
       </c>
       <c r="C49">
-        <v>1648.677093219934</v>
+        <v>1632.722627097551</v>
       </c>
       <c r="D49">
-        <v>2665.353093219935</v>
+        <v>2673.406627097551</v>
       </c>
       <c r="E49">
-        <v>981.4760000000002</v>
+        <v>1005.484</v>
       </c>
       <c r="F49">
-        <v>1128.376</v>
+        <v>1152.384</v>
       </c>
       <c r="G49">
         <v>111.7</v>
@@ -5305,28 +5305,28 @@
         <v>445.3</v>
       </c>
       <c r="M49">
-        <v>61.27081680000001</v>
+        <v>62.57445120000001</v>
       </c>
       <c r="N49">
-        <v>384.0291832</v>
+        <v>382.7255488</v>
       </c>
       <c r="O49">
-        <v>96.00729579999999</v>
+        <v>95.6813872</v>
       </c>
       <c r="P49">
-        <v>288.0218874</v>
+        <v>287.0441616</v>
       </c>
       <c r="Q49">
-        <v>426.8218874</v>
+        <v>425.8441616</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2190218741756599</v>
+        <v>0.2218529137405269</v>
       </c>
       <c r="T49">
-        <v>1.059403418981592</v>
+        <v>1.076717704539147</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.267734025050567</v>
+        <v>7.116322899528681</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.134911515145074</v>
+        <v>0.1346006869770482</v>
       </c>
       <c r="C50">
-        <v>1632.722627097551</v>
+        <v>1616.816977005479</v>
       </c>
       <c r="D50">
-        <v>2673.406627097551</v>
+        <v>2681.508977005479</v>
       </c>
       <c r="E50">
-        <v>1005.484</v>
+        <v>1029.492</v>
       </c>
       <c r="F50">
-        <v>1152.384</v>
+        <v>1176.392</v>
       </c>
       <c r="G50">
         <v>111.7</v>
@@ -5387,28 +5387,28 @@
         <v>445.3</v>
       </c>
       <c r="M50">
-        <v>62.5744512</v>
+        <v>63.87808560000001</v>
       </c>
       <c r="N50">
-        <v>382.7255488</v>
+        <v>381.4219144</v>
       </c>
       <c r="O50">
-        <v>95.6813872</v>
+        <v>95.3554786</v>
       </c>
       <c r="P50">
-        <v>287.0441616</v>
+        <v>286.0664358</v>
       </c>
       <c r="Q50">
-        <v>425.8441616</v>
+        <v>424.8664358</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2218529137405269</v>
+        <v>0.2247949744648004</v>
       </c>
       <c r="T50">
-        <v>1.076717704539147</v>
+        <v>1.094710981687194</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.116322899528682</v>
+        <v>6.971091819946463</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1346006869770482</v>
+        <v>0.1342898588090224</v>
       </c>
       <c r="C51">
-        <v>1616.816977005479</v>
+        <v>1600.960588136294</v>
       </c>
       <c r="D51">
-        <v>2681.508977005479</v>
+        <v>2689.660588136294</v>
       </c>
       <c r="E51">
-        <v>1029.492</v>
+        <v>1053.5</v>
       </c>
       <c r="F51">
-        <v>1176.392</v>
+        <v>1200.4</v>
       </c>
       <c r="G51">
         <v>111.7</v>
@@ -5469,28 +5469,28 @@
         <v>445.3</v>
       </c>
       <c r="M51">
-        <v>63.87808560000001</v>
+        <v>65.18172000000001</v>
       </c>
       <c r="N51">
-        <v>381.4219144</v>
+        <v>380.11828</v>
       </c>
       <c r="O51">
-        <v>95.3554786</v>
+        <v>95.02957000000001</v>
       </c>
       <c r="P51">
-        <v>286.0664358</v>
+        <v>285.08871</v>
       </c>
       <c r="Q51">
-        <v>424.8664358</v>
+        <v>423.88871</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2247949744648004</v>
+        <v>0.2278547176180449</v>
       </c>
       <c r="T51">
-        <v>1.094710981687194</v>
+        <v>1.113423989921164</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.971091819946463</v>
+        <v>6.831669983547534</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1342898588090224</v>
+        <v>0.1339790306409967</v>
       </c>
       <c r="C52">
-        <v>1600.960588136294</v>
+        <v>1585.153911112503</v>
       </c>
       <c r="D52">
-        <v>2689.660588136294</v>
+        <v>2697.861911112503</v>
       </c>
       <c r="E52">
-        <v>1053.5</v>
+        <v>1077.508</v>
       </c>
       <c r="F52">
-        <v>1200.4</v>
+        <v>1224.408</v>
       </c>
       <c r="G52">
         <v>111.7</v>
@@ -5551,28 +5551,28 @@
         <v>445.3</v>
       </c>
       <c r="M52">
-        <v>65.18172000000001</v>
+        <v>66.48535440000001</v>
       </c>
       <c r="N52">
-        <v>380.11828</v>
+        <v>378.8146456</v>
       </c>
       <c r="O52">
-        <v>95.02957000000001</v>
+        <v>94.7036614</v>
       </c>
       <c r="P52">
-        <v>285.08871</v>
+        <v>284.1109842</v>
       </c>
       <c r="Q52">
-        <v>423.88871</v>
+        <v>422.9109842</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2278547176180449</v>
+        <v>0.231039348246932</v>
       </c>
       <c r="T52">
-        <v>1.113423989921164</v>
+        <v>1.132900794409581</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.831669983547534</v>
+        <v>6.697715670144642</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1339790306409967</v>
+        <v>0.1336682024729709</v>
       </c>
       <c r="C53">
-        <v>1585.153911112503</v>
+        <v>1569.397402069584</v>
       </c>
       <c r="D53">
-        <v>2697.861911112503</v>
+        <v>2706.113402069584</v>
       </c>
       <c r="E53">
-        <v>1077.508</v>
+        <v>1101.516</v>
       </c>
       <c r="F53">
-        <v>1224.408</v>
+        <v>1248.416</v>
       </c>
       <c r="G53">
         <v>111.7</v>
@@ -5633,28 +5633,28 @@
         <v>445.3</v>
       </c>
       <c r="M53">
-        <v>66.48535440000001</v>
+        <v>67.78898880000001</v>
       </c>
       <c r="N53">
-        <v>378.8146456</v>
+        <v>377.5110112</v>
       </c>
       <c r="O53">
-        <v>94.7036614</v>
+        <v>94.3777528</v>
       </c>
       <c r="P53">
-        <v>284.1109842</v>
+        <v>283.1332584</v>
       </c>
       <c r="Q53">
-        <v>422.9109842</v>
+        <v>421.9332584</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.231039348246932</v>
+        <v>0.2343566718186894</v>
       </c>
       <c r="T53">
-        <v>1.132900794409581</v>
+        <v>1.153189132418348</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.697715670144642</v>
+        <v>6.568913445718782</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1336682024729709</v>
+        <v>0.1333573743049451</v>
       </c>
       <c r="C54">
-        <v>1569.397402069584</v>
+        <v>1553.691522740547</v>
       </c>
       <c r="D54">
-        <v>2706.113402069584</v>
+        <v>2714.415522740547</v>
       </c>
       <c r="E54">
-        <v>1101.516</v>
+        <v>1125.524</v>
       </c>
       <c r="F54">
-        <v>1248.416</v>
+        <v>1272.424</v>
       </c>
       <c r="G54">
         <v>111.7</v>
@@ -5715,28 +5715,28 @@
         <v>445.3</v>
       </c>
       <c r="M54">
-        <v>67.78898880000001</v>
+        <v>69.09262320000001</v>
       </c>
       <c r="N54">
-        <v>377.5110112</v>
+        <v>376.2073768</v>
       </c>
       <c r="O54">
-        <v>94.3777528</v>
+        <v>94.05184420000001</v>
       </c>
       <c r="P54">
-        <v>283.1332584</v>
+        <v>282.1555326</v>
       </c>
       <c r="Q54">
-        <v>421.9332584</v>
+        <v>420.9555326</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2343566718186894</v>
+        <v>0.2378151580956279</v>
       </c>
       <c r="T54">
-        <v>1.153189132418348</v>
+        <v>1.174340803959404</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.568913445718782</v>
+        <v>6.444971682592014</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1333573743049451</v>
+        <v>0.1330465461369193</v>
       </c>
       <c r="C55">
-        <v>1553.691522740547</v>
+        <v>1538.036740542069</v>
       </c>
       <c r="D55">
-        <v>2714.415522740547</v>
+        <v>2722.76874054207</v>
       </c>
       <c r="E55">
-        <v>1125.524</v>
+        <v>1149.532</v>
       </c>
       <c r="F55">
-        <v>1272.424</v>
+        <v>1296.432</v>
       </c>
       <c r="G55">
         <v>111.7</v>
@@ -5797,28 +5797,28 @@
         <v>445.3</v>
       </c>
       <c r="M55">
-        <v>69.09262320000001</v>
+        <v>70.39625760000001</v>
       </c>
       <c r="N55">
-        <v>376.2073768</v>
+        <v>374.9037424</v>
       </c>
       <c r="O55">
-        <v>94.05184420000001</v>
+        <v>93.7259356</v>
       </c>
       <c r="P55">
-        <v>282.1555326</v>
+        <v>281.1778068</v>
       </c>
       <c r="Q55">
-        <v>420.9555326</v>
+        <v>419.9778068</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2378151580956279</v>
+        <v>0.241424013341129</v>
       </c>
       <c r="T55">
-        <v>1.174340803959404</v>
+        <v>1.196412113393549</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.444971682592014</v>
+        <v>6.325620355136605</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1330465461369193</v>
+        <v>0.1327357179688936</v>
       </c>
       <c r="C56">
-        <v>1538.036740542069</v>
+        <v>1522.433528662215</v>
       </c>
       <c r="D56">
-        <v>2722.76874054207</v>
+        <v>2731.173528662216</v>
       </c>
       <c r="E56">
-        <v>1149.532</v>
+        <v>1173.54</v>
       </c>
       <c r="F56">
-        <v>1296.432</v>
+        <v>1320.44</v>
       </c>
       <c r="G56">
         <v>111.7</v>
@@ -5879,28 +5879,28 @@
         <v>445.3</v>
       </c>
       <c r="M56">
-        <v>70.39625760000001</v>
+        <v>71.69989200000002</v>
       </c>
       <c r="N56">
-        <v>374.9037424</v>
+        <v>373.600108</v>
       </c>
       <c r="O56">
-        <v>93.7259356</v>
+        <v>93.40002699999999</v>
       </c>
       <c r="P56">
-        <v>281.1778068</v>
+        <v>280.200081</v>
       </c>
       <c r="Q56">
-        <v>419.9778068</v>
+        <v>419.000081</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.241424013341129</v>
+        <v>0.2451932621530968</v>
       </c>
       <c r="T56">
-        <v>1.196412113393549</v>
+        <v>1.219464369913656</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.325620355136605</v>
+        <v>6.210609075952302</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1327357179688936</v>
+        <v>0.1328448898008678</v>
       </c>
       <c r="C57">
-        <v>1522.433528662215</v>
+        <v>1495.467618810139</v>
       </c>
       <c r="D57">
-        <v>2731.173528662216</v>
+        <v>2728.215618810139</v>
       </c>
       <c r="E57">
-        <v>1173.54</v>
+        <v>1197.548</v>
       </c>
       <c r="F57">
-        <v>1320.44</v>
+        <v>1344.448</v>
       </c>
       <c r="G57">
         <v>111.7</v>
@@ -5961,45 +5961,45 @@
         <v>445.3</v>
       </c>
       <c r="M57">
-        <v>71.69989200000002</v>
+        <v>74.34797440000003</v>
       </c>
       <c r="N57">
-        <v>373.600108</v>
+        <v>370.9520256</v>
       </c>
       <c r="O57">
-        <v>93.40002699999999</v>
+        <v>92.73800639999999</v>
       </c>
       <c r="P57">
-        <v>280.200081</v>
+        <v>278.2140191999999</v>
       </c>
       <c r="Q57">
-        <v>419.000081</v>
+        <v>417.0140192</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2451932621530968</v>
+        <v>0.2491338404565177</v>
       </c>
       <c r="T57">
-        <v>1.219464369913656</v>
+        <v>1.243564456275585</v>
       </c>
       <c r="U57">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>6.210609075952302</v>
+        <v>5.989403256694507</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1328448898008678</v>
+        <v>0.132541561632842</v>
       </c>
       <c r="C58">
-        <v>1495.467618810139</v>
+        <v>1479.693892227609</v>
       </c>
       <c r="D58">
-        <v>2728.215618810139</v>
+        <v>2736.44989222761</v>
       </c>
       <c r="E58">
-        <v>1197.548</v>
+        <v>1221.556</v>
       </c>
       <c r="F58">
-        <v>1344.448</v>
+        <v>1368.456</v>
       </c>
       <c r="G58">
         <v>111.7</v>
@@ -6043,28 +6043,28 @@
         <v>445.3</v>
       </c>
       <c r="M58">
-        <v>74.34797440000003</v>
+        <v>75.67561680000003</v>
       </c>
       <c r="N58">
-        <v>370.9520256</v>
+        <v>369.6243832</v>
       </c>
       <c r="O58">
-        <v>92.73800639999999</v>
+        <v>92.4060958</v>
       </c>
       <c r="P58">
-        <v>278.2140191999999</v>
+        <v>277.2182874</v>
       </c>
       <c r="Q58">
-        <v>417.0140192</v>
+        <v>416.0182874</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2491338404565177</v>
+        <v>0.2532577014717255</v>
       </c>
       <c r="T58">
-        <v>1.243564456275585</v>
+        <v>1.268785476886908</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.989403256694507</v>
+        <v>5.88432600657706</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.132541561632842</v>
+        <v>0.1322382334648162</v>
       </c>
       <c r="C59">
-        <v>1479.693892227609</v>
+        <v>1463.970021324294</v>
       </c>
       <c r="D59">
-        <v>2736.44989222761</v>
+        <v>2744.734021324295</v>
       </c>
       <c r="E59">
-        <v>1221.556</v>
+        <v>1245.564</v>
       </c>
       <c r="F59">
-        <v>1368.456</v>
+        <v>1392.464</v>
       </c>
       <c r="G59">
         <v>111.7</v>
@@ -6125,28 +6125,28 @@
         <v>445.3</v>
       </c>
       <c r="M59">
-        <v>75.67561680000003</v>
+        <v>77.00325920000002</v>
       </c>
       <c r="N59">
-        <v>369.6243832</v>
+        <v>368.2967408</v>
       </c>
       <c r="O59">
-        <v>92.4060958</v>
+        <v>92.0741852</v>
       </c>
       <c r="P59">
-        <v>277.2182874</v>
+        <v>276.2225556</v>
       </c>
       <c r="Q59">
-        <v>416.0182874</v>
+        <v>415.0225556</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2532577014717255</v>
+        <v>0.257577936820991</v>
       </c>
       <c r="T59">
-        <v>1.268785476886908</v>
+        <v>1.295207498479721</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.88432600657706</v>
+        <v>5.782872109911939</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1322382334648162</v>
+        <v>0.1319349052967904</v>
       </c>
       <c r="C60">
-        <v>1463.970021324295</v>
+        <v>1448.29646026345</v>
       </c>
       <c r="D60">
-        <v>2744.734021324295</v>
+        <v>2753.068460263451</v>
       </c>
       <c r="E60">
-        <v>1245.564</v>
+        <v>1269.572</v>
       </c>
       <c r="F60">
-        <v>1392.464</v>
+        <v>1416.472</v>
       </c>
       <c r="G60">
         <v>111.7</v>
@@ -6207,28 +6207,28 @@
         <v>445.3</v>
       </c>
       <c r="M60">
-        <v>77.0032592</v>
+        <v>78.3309016</v>
       </c>
       <c r="N60">
-        <v>368.2967408</v>
+        <v>366.9690984</v>
       </c>
       <c r="O60">
-        <v>92.0741852</v>
+        <v>91.7422746</v>
       </c>
       <c r="P60">
-        <v>276.2225556</v>
+        <v>275.2268238</v>
       </c>
       <c r="Q60">
-        <v>415.0225556</v>
+        <v>414.0268238</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2575779368209909</v>
+        <v>0.2621089153580254</v>
       </c>
       <c r="T60">
-        <v>1.295207498479721</v>
+        <v>1.322918399174623</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.78287210991194</v>
+        <v>5.684857328388008</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1319349052967904</v>
+        <v>0.1316315771287647</v>
       </c>
       <c r="C61">
-        <v>1448.29646026345</v>
+        <v>1432.67366874144</v>
       </c>
       <c r="D61">
-        <v>2753.068460263451</v>
+        <v>2761.453668741441</v>
       </c>
       <c r="E61">
-        <v>1269.572</v>
+        <v>1293.58</v>
       </c>
       <c r="F61">
-        <v>1416.472</v>
+        <v>1440.48</v>
       </c>
       <c r="G61">
         <v>111.7</v>
@@ -6289,28 +6289,28 @@
         <v>445.3</v>
       </c>
       <c r="M61">
-        <v>78.3309016</v>
+        <v>79.65854400000001</v>
       </c>
       <c r="N61">
-        <v>366.9690984</v>
+        <v>365.641456</v>
       </c>
       <c r="O61">
-        <v>91.7422746</v>
+        <v>91.410364</v>
       </c>
       <c r="P61">
-        <v>275.2268238</v>
+        <v>274.231092</v>
       </c>
       <c r="Q61">
-        <v>414.0268238</v>
+        <v>413.031092</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2621089153580254</v>
+        <v>0.2668664428219116</v>
       </c>
       <c r="T61">
-        <v>1.322918399174623</v>
+        <v>1.35201484490427</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.684857328388008</v>
+        <v>5.590109706248208</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1316315771287647</v>
+        <v>0.1313282489607389</v>
       </c>
       <c r="C62">
-        <v>1432.67366874144</v>
+        <v>1417.102112072249</v>
       </c>
       <c r="D62">
-        <v>2761.453668741441</v>
+        <v>2769.890112072249</v>
       </c>
       <c r="E62">
-        <v>1293.58</v>
+        <v>1317.588</v>
       </c>
       <c r="F62">
-        <v>1440.48</v>
+        <v>1464.488</v>
       </c>
       <c r="G62">
         <v>111.7</v>
@@ -6371,28 +6371,28 @@
         <v>445.3</v>
       </c>
       <c r="M62">
-        <v>79.65854400000001</v>
+        <v>80.98618640000001</v>
       </c>
       <c r="N62">
-        <v>365.641456</v>
+        <v>364.3138136</v>
       </c>
       <c r="O62">
-        <v>91.410364</v>
+        <v>91.0784534</v>
       </c>
       <c r="P62">
-        <v>274.231092</v>
+        <v>273.2353602</v>
       </c>
       <c r="Q62">
-        <v>413.031092</v>
+        <v>412.0353602</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2668664428219116</v>
+        <v>0.2718679460531766</v>
       </c>
       <c r="T62">
-        <v>1.35201484490427</v>
+        <v>1.382603416055951</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.590109706248208</v>
+        <v>5.498468563522827</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1313282489607389</v>
+        <v>0.1310249207927131</v>
       </c>
       <c r="C63">
-        <v>1417.102112072249</v>
+        <v>1401.58226127356</v>
       </c>
       <c r="D63">
-        <v>2769.890112072249</v>
+        <v>2778.37826127356</v>
       </c>
       <c r="E63">
-        <v>1317.588</v>
+        <v>1341.596</v>
       </c>
       <c r="F63">
-        <v>1464.488</v>
+        <v>1488.496</v>
       </c>
       <c r="G63">
         <v>111.7</v>
@@ -6453,28 +6453,28 @@
         <v>445.3</v>
       </c>
       <c r="M63">
-        <v>80.98618640000001</v>
+        <v>82.31382880000001</v>
       </c>
       <c r="N63">
-        <v>364.3138136</v>
+        <v>362.9861712</v>
       </c>
       <c r="O63">
-        <v>91.0784534</v>
+        <v>90.7465428</v>
       </c>
       <c r="P63">
-        <v>273.2353602</v>
+        <v>272.2396284</v>
       </c>
       <c r="Q63">
-        <v>412.0353602</v>
+        <v>411.0396284</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2718679460531766</v>
+        <v>0.2771326862966134</v>
       </c>
       <c r="T63">
-        <v>1.382603416055951</v>
+        <v>1.414801912005088</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.498468563522827</v>
+        <v>5.409783586691814</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1310249207927131</v>
+        <v>0.1307215926246873</v>
       </c>
       <c r="C64">
-        <v>1401.58226127356</v>
+        <v>1386.114593154418</v>
       </c>
       <c r="D64">
-        <v>2778.37826127356</v>
+        <v>2786.918593154418</v>
       </c>
       <c r="E64">
-        <v>1341.596</v>
+        <v>1365.604</v>
       </c>
       <c r="F64">
-        <v>1488.496</v>
+        <v>1512.504</v>
       </c>
       <c r="G64">
         <v>111.7</v>
@@ -6535,28 +6535,28 @@
         <v>445.3</v>
       </c>
       <c r="M64">
-        <v>82.31382880000001</v>
+        <v>83.64147120000001</v>
       </c>
       <c r="N64">
-        <v>362.9861712</v>
+        <v>361.6585288</v>
       </c>
       <c r="O64">
-        <v>90.7465428</v>
+        <v>90.4146322</v>
       </c>
       <c r="P64">
-        <v>272.2396284</v>
+        <v>271.2438966</v>
       </c>
       <c r="Q64">
-        <v>411.0396284</v>
+        <v>410.0438966</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2771326862966134</v>
+        <v>0.2826820070937495</v>
       </c>
       <c r="T64">
-        <v>1.414801912005088</v>
+        <v>1.448740867194719</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.409783586691814</v>
+        <v>5.323914005950674</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1307215926246873</v>
+        <v>0.1304182644566615</v>
       </c>
       <c r="C65">
-        <v>1386.114593154418</v>
+        <v>1370.699590404509</v>
       </c>
       <c r="D65">
-        <v>2786.918593154418</v>
+        <v>2795.51159040451</v>
       </c>
       <c r="E65">
-        <v>1365.604</v>
+        <v>1389.612</v>
       </c>
       <c r="F65">
-        <v>1512.504</v>
+        <v>1536.512</v>
       </c>
       <c r="G65">
         <v>111.7</v>
@@ -6617,28 +6617,28 @@
         <v>445.3</v>
       </c>
       <c r="M65">
-        <v>83.64147120000001</v>
+        <v>84.96911360000001</v>
       </c>
       <c r="N65">
-        <v>361.6585288</v>
+        <v>360.3308864</v>
       </c>
       <c r="O65">
-        <v>90.4146322</v>
+        <v>90.0827216</v>
       </c>
       <c r="P65">
-        <v>271.2438966</v>
+        <v>270.2481648</v>
       </c>
       <c r="Q65">
-        <v>410.0438966</v>
+        <v>409.0481648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2826820070937495</v>
+        <v>0.2885396234907265</v>
       </c>
       <c r="T65">
-        <v>1.448740867194719</v>
+        <v>1.484565319894885</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.323914005950674</v>
+        <v>5.240727849607695</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1304182644566615</v>
+        <v>0.1301149362886358</v>
       </c>
       <c r="C66">
-        <v>1370.699590404509</v>
+        <v>1355.337741685107</v>
       </c>
       <c r="D66">
-        <v>2795.51159040451</v>
+        <v>2804.157741685107</v>
       </c>
       <c r="E66">
-        <v>1389.612</v>
+        <v>1413.62</v>
       </c>
       <c r="F66">
-        <v>1536.512</v>
+        <v>1560.52</v>
       </c>
       <c r="G66">
         <v>111.7</v>
@@ -6699,28 +6699,28 @@
         <v>445.3</v>
       </c>
       <c r="M66">
-        <v>84.96911360000001</v>
+        <v>86.29675600000002</v>
       </c>
       <c r="N66">
-        <v>360.3308864</v>
+        <v>359.003244</v>
       </c>
       <c r="O66">
-        <v>90.0827216</v>
+        <v>89.750811</v>
       </c>
       <c r="P66">
-        <v>270.2481648</v>
+        <v>269.252433</v>
       </c>
       <c r="Q66">
-        <v>409.0481648</v>
+        <v>408.052433</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2885396234907265</v>
+        <v>0.2947319608246736</v>
       </c>
       <c r="T66">
-        <v>1.484565319894885</v>
+        <v>1.522436884177918</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.240727849607695</v>
+        <v>5.160101267306038</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1301149362886358</v>
+        <v>0.12981160812061</v>
       </c>
       <c r="C67">
-        <v>1355.337741685107</v>
+        <v>1340.029541721699</v>
       </c>
       <c r="D67">
-        <v>2804.157741685107</v>
+        <v>2812.8575417217</v>
       </c>
       <c r="E67">
-        <v>1413.62</v>
+        <v>1437.628</v>
       </c>
       <c r="F67">
-        <v>1560.52</v>
+        <v>1584.528</v>
       </c>
       <c r="G67">
         <v>111.7</v>
@@ -6781,28 +6781,28 @@
         <v>445.3</v>
       </c>
       <c r="M67">
-        <v>86.29675600000002</v>
+        <v>87.62439840000002</v>
       </c>
       <c r="N67">
-        <v>359.003244</v>
+        <v>357.6756016</v>
       </c>
       <c r="O67">
-        <v>89.750811</v>
+        <v>89.4189004</v>
       </c>
       <c r="P67">
-        <v>269.252433</v>
+        <v>268.2567012</v>
       </c>
       <c r="Q67">
-        <v>408.052433</v>
+        <v>407.0567012</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2947319608246736</v>
+        <v>0.3012885532959118</v>
       </c>
       <c r="T67">
-        <v>1.522436884177918</v>
+        <v>1.562536187536423</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.160101267306038</v>
+        <v>5.081917914771098</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.12981160812061</v>
+        <v>0.1295082799525842</v>
       </c>
       <c r="C68">
-        <v>1340.029541721699</v>
+        <v>1324.775491398356</v>
       </c>
       <c r="D68">
-        <v>2812.8575417217</v>
+        <v>2821.611491398357</v>
       </c>
       <c r="E68">
-        <v>1437.628</v>
+        <v>1461.636</v>
       </c>
       <c r="F68">
-        <v>1584.528</v>
+        <v>1608.536</v>
       </c>
       <c r="G68">
         <v>111.7</v>
@@ -6863,28 +6863,28 @@
         <v>445.3</v>
       </c>
       <c r="M68">
-        <v>87.62439840000002</v>
+        <v>88.95204080000002</v>
       </c>
       <c r="N68">
-        <v>357.6756016</v>
+        <v>356.3479592</v>
       </c>
       <c r="O68">
-        <v>89.4189004</v>
+        <v>89.0869898</v>
       </c>
       <c r="P68">
-        <v>268.2567012</v>
+        <v>267.2609694</v>
       </c>
       <c r="Q68">
-        <v>407.0567012</v>
+        <v>406.0609694</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3012885532959118</v>
+        <v>0.308242515007831</v>
       </c>
       <c r="T68">
-        <v>1.562536187536423</v>
+        <v>1.605065751704535</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.081917914771098</v>
+        <v>5.006068393655111</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1295082799525842</v>
+        <v>0.1292049517845584</v>
       </c>
       <c r="C69">
-        <v>1324.775491398356</v>
+        <v>1309.576097853856</v>
       </c>
       <c r="D69">
-        <v>2821.611491398357</v>
+        <v>2830.420097853856</v>
       </c>
       <c r="E69">
-        <v>1461.636</v>
+        <v>1485.644</v>
       </c>
       <c r="F69">
-        <v>1608.536</v>
+        <v>1632.544</v>
       </c>
       <c r="G69">
         <v>111.7</v>
@@ -6945,28 +6945,28 @@
         <v>445.3</v>
       </c>
       <c r="M69">
-        <v>88.95204080000002</v>
+        <v>90.27968320000002</v>
       </c>
       <c r="N69">
-        <v>356.3479592</v>
+        <v>355.0203168</v>
       </c>
       <c r="O69">
-        <v>89.0869898</v>
+        <v>88.7550792</v>
       </c>
       <c r="P69">
-        <v>267.2609694</v>
+        <v>266.2652376</v>
       </c>
       <c r="Q69">
-        <v>406.0609694</v>
+        <v>405.0652376</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.308242515007831</v>
+        <v>0.3156310993267451</v>
       </c>
       <c r="T69">
-        <v>1.605065751704535</v>
+        <v>1.650253413633153</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.006068393655111</v>
+        <v>4.932449740807241</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1292049517845584</v>
+        <v>0.1289016236165327</v>
       </c>
       <c r="C70">
-        <v>1309.576097853856</v>
+        <v>1294.431874579623</v>
       </c>
       <c r="D70">
-        <v>2830.420097853856</v>
+        <v>2839.283874579623</v>
       </c>
       <c r="E70">
-        <v>1485.644</v>
+        <v>1509.652</v>
       </c>
       <c r="F70">
-        <v>1632.544</v>
+        <v>1656.552</v>
       </c>
       <c r="G70">
         <v>111.7</v>
@@ -7027,28 +7027,28 @@
         <v>445.3</v>
       </c>
       <c r="M70">
-        <v>90.27968320000002</v>
+        <v>91.60732560000002</v>
       </c>
       <c r="N70">
-        <v>355.0203168</v>
+        <v>353.6926744</v>
       </c>
       <c r="O70">
-        <v>88.7550792</v>
+        <v>88.4231686</v>
       </c>
       <c r="P70">
-        <v>266.2652376</v>
+        <v>265.2695058</v>
       </c>
       <c r="Q70">
-        <v>405.0652376</v>
+        <v>404.0695058</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3156310993267451</v>
+        <v>0.3234963665049441</v>
       </c>
       <c r="T70">
-        <v>1.650253413633153</v>
+        <v>1.698356408589425</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.932449740807241</v>
+        <v>4.860964961954963</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1289016236165327</v>
+        <v>0.1285982954485069</v>
       </c>
       <c r="C71">
-        <v>1294.431874579623</v>
+        <v>1279.343341519515</v>
       </c>
       <c r="D71">
-        <v>2839.283874579623</v>
+        <v>2848.203341519516</v>
       </c>
       <c r="E71">
-        <v>1509.652</v>
+        <v>1533.66</v>
       </c>
       <c r="F71">
-        <v>1656.552</v>
+        <v>1680.56</v>
       </c>
       <c r="G71">
         <v>111.7</v>
@@ -7109,28 +7109,28 @@
         <v>445.3</v>
       </c>
       <c r="M71">
-        <v>91.60732560000002</v>
+        <v>92.93496800000003</v>
       </c>
       <c r="N71">
-        <v>353.6926744</v>
+        <v>352.365032</v>
       </c>
       <c r="O71">
-        <v>88.4231686</v>
+        <v>88.091258</v>
       </c>
       <c r="P71">
-        <v>265.2695058</v>
+        <v>264.273774</v>
       </c>
       <c r="Q71">
-        <v>404.0695058</v>
+        <v>403.073774</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3234963665049441</v>
+        <v>0.3318859848283563</v>
       </c>
       <c r="T71">
-        <v>1.698356408589425</v>
+        <v>1.749666269876115</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.860964961954963</v>
+        <v>4.791522605355606</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1285982954485069</v>
+        <v>0.1282949672804811</v>
       </c>
       <c r="C72">
-        <v>1279.343341519515</v>
+        <v>1264.311025171487</v>
       </c>
       <c r="D72">
-        <v>2848.203341519516</v>
+        <v>2857.179025171487</v>
       </c>
       <c r="E72">
-        <v>1533.66</v>
+        <v>1557.668</v>
       </c>
       <c r="F72">
-        <v>1680.56</v>
+        <v>1704.568</v>
       </c>
       <c r="G72">
         <v>111.7</v>
@@ -7191,28 +7191,28 @@
         <v>445.3</v>
       </c>
       <c r="M72">
-        <v>92.93496800000003</v>
+        <v>94.26261040000001</v>
       </c>
       <c r="N72">
-        <v>352.365032</v>
+        <v>351.0373896</v>
       </c>
       <c r="O72">
-        <v>88.091258</v>
+        <v>87.7593474</v>
       </c>
       <c r="P72">
-        <v>264.273774</v>
+        <v>263.2780422</v>
       </c>
       <c r="Q72">
-        <v>403.073774</v>
+        <v>402.0780422</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3318859848283563</v>
+        <v>0.3408541975189004</v>
       </c>
       <c r="T72">
-        <v>1.749666269876115</v>
+        <v>1.804514742286024</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.791522605355606</v>
+        <v>4.724036371477359</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1282949672804811</v>
+        <v>0.1279916391124553</v>
       </c>
       <c r="C73">
-        <v>1264.311025171487</v>
+        <v>1249.33545869119</v>
       </c>
       <c r="D73">
-        <v>2857.179025171487</v>
+        <v>2866.21145869119</v>
       </c>
       <c r="E73">
-        <v>1557.668</v>
+        <v>1581.676</v>
       </c>
       <c r="F73">
-        <v>1704.568</v>
+        <v>1728.576</v>
       </c>
       <c r="G73">
         <v>111.7</v>
@@ -7273,28 +7273,28 @@
         <v>445.3</v>
       </c>
       <c r="M73">
-        <v>94.2626104</v>
+        <v>95.5902528</v>
       </c>
       <c r="N73">
-        <v>351.0373896</v>
+        <v>349.7097472</v>
       </c>
       <c r="O73">
-        <v>87.7593474</v>
+        <v>87.42743680000001</v>
       </c>
       <c r="P73">
-        <v>263.2780422</v>
+        <v>262.2823104</v>
       </c>
       <c r="Q73">
-        <v>402.0780422</v>
+        <v>401.0823104</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3408541975189003</v>
+        <v>0.3504629968301975</v>
       </c>
       <c r="T73">
-        <v>1.804514742286024</v>
+        <v>1.863280962725212</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.724036371477359</v>
+        <v>4.658424755206841</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1279916391124553</v>
+        <v>0.1276883109444295</v>
       </c>
       <c r="C74">
-        <v>1249.33545869119</v>
+        <v>1234.417181997539</v>
       </c>
       <c r="D74">
-        <v>2866.21145869119</v>
+        <v>2875.30118199754</v>
       </c>
       <c r="E74">
-        <v>1581.676</v>
+        <v>1605.684</v>
       </c>
       <c r="F74">
-        <v>1728.576</v>
+        <v>1752.584</v>
       </c>
       <c r="G74">
         <v>111.7</v>
@@ -7355,28 +7355,28 @@
         <v>445.3</v>
       </c>
       <c r="M74">
-        <v>95.5902528</v>
+        <v>96.9178952</v>
       </c>
       <c r="N74">
-        <v>349.7097472</v>
+        <v>348.3821048</v>
       </c>
       <c r="O74">
-        <v>87.42743680000001</v>
+        <v>87.09552619999999</v>
       </c>
       <c r="P74">
-        <v>262.2823104</v>
+        <v>261.2865786</v>
       </c>
       <c r="Q74">
-        <v>401.0823104</v>
+        <v>400.0865786</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3504629968301975</v>
+        <v>0.3607835590534427</v>
       </c>
       <c r="T74">
-        <v>1.863280962725212</v>
+        <v>1.926400236530267</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.658424755206841</v>
+        <v>4.594610717464281</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1276883109444295</v>
+        <v>0.1273849827764038</v>
       </c>
       <c r="C75">
-        <v>1234.417181997539</v>
+        <v>1219.556741880303</v>
       </c>
       <c r="D75">
-        <v>2875.30118199754</v>
+        <v>2884.448741880303</v>
       </c>
       <c r="E75">
-        <v>1605.684</v>
+        <v>1629.692</v>
       </c>
       <c r="F75">
-        <v>1752.584</v>
+        <v>1776.592</v>
       </c>
       <c r="G75">
         <v>111.7</v>
@@ -7437,28 +7437,28 @@
         <v>445.3</v>
       </c>
       <c r="M75">
-        <v>96.9178952</v>
+        <v>98.24553760000001</v>
       </c>
       <c r="N75">
-        <v>348.3821048</v>
+        <v>347.0544624</v>
       </c>
       <c r="O75">
-        <v>87.09552619999999</v>
+        <v>86.76361560000001</v>
       </c>
       <c r="P75">
-        <v>261.2865786</v>
+        <v>260.2908468000001</v>
       </c>
       <c r="Q75">
-        <v>400.0865786</v>
+        <v>399.0908468000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3607835590534427</v>
+        <v>0.3718980106784759</v>
       </c>
       <c r="T75">
-        <v>1.926400236530267</v>
+        <v>1.994374839089557</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.594610717464281</v>
+        <v>4.532521383444493</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1273849827764038</v>
+        <v>0.128487904608378</v>
       </c>
       <c r="C76">
-        <v>1219.556741880303</v>
+        <v>1162.563345827002</v>
       </c>
       <c r="D76">
-        <v>2884.448741880303</v>
+        <v>2851.463345827002</v>
       </c>
       <c r="E76">
-        <v>1629.692</v>
+        <v>1653.7</v>
       </c>
       <c r="F76">
-        <v>1776.592</v>
+        <v>1800.6</v>
       </c>
       <c r="G76">
         <v>111.7</v>
@@ -7519,45 +7519,45 @@
         <v>445.3</v>
       </c>
       <c r="M76">
-        <v>98.24553760000001</v>
+        <v>104.07468</v>
       </c>
       <c r="N76">
-        <v>347.0544624</v>
+        <v>341.22532</v>
       </c>
       <c r="O76">
-        <v>86.76361560000001</v>
+        <v>85.30633</v>
       </c>
       <c r="P76">
-        <v>260.2908468000001</v>
+        <v>255.91899</v>
       </c>
       <c r="Q76">
-        <v>399.0908468000001</v>
+        <v>394.71899</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3718980106784759</v>
+        <v>0.3839016184335119</v>
       </c>
       <c r="T76">
-        <v>1.994374839089557</v>
+        <v>2.06778740985359</v>
       </c>
       <c r="U76">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.532521383444493</v>
+        <v>4.278658363398282</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.128487904608378</v>
+        <v>0.1282033264403522</v>
       </c>
       <c r="C77">
-        <v>1162.563345827002</v>
+        <v>1146.993876935996</v>
       </c>
       <c r="D77">
-        <v>2851.463345827002</v>
+        <v>2859.901876935996</v>
       </c>
       <c r="E77">
-        <v>1653.7</v>
+        <v>1677.708</v>
       </c>
       <c r="F77">
-        <v>1800.6</v>
+        <v>1824.608</v>
       </c>
       <c r="G77">
         <v>111.7</v>
@@ -7601,28 +7601,28 @@
         <v>445.3</v>
       </c>
       <c r="M77">
-        <v>104.07468</v>
+        <v>105.4623424</v>
       </c>
       <c r="N77">
-        <v>341.22532</v>
+        <v>339.8376576</v>
       </c>
       <c r="O77">
-        <v>85.30633</v>
+        <v>84.9594144</v>
       </c>
       <c r="P77">
-        <v>255.91899</v>
+        <v>254.8782432</v>
       </c>
       <c r="Q77">
-        <v>394.71899</v>
+        <v>393.6782432</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3839016184335119</v>
+        <v>0.3969055268348008</v>
       </c>
       <c r="T77">
-        <v>2.06778740985359</v>
+        <v>2.147317694847958</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.278658363398282</v>
+        <v>4.222360227037779</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1282033264403522</v>
+        <v>0.1279187482723264</v>
       </c>
       <c r="C78">
-        <v>1146.993876935996</v>
+        <v>1131.474501738796</v>
       </c>
       <c r="D78">
-        <v>2859.901876935996</v>
+        <v>2868.390501738796</v>
       </c>
       <c r="E78">
-        <v>1677.708</v>
+        <v>1701.716</v>
       </c>
       <c r="F78">
-        <v>1824.608</v>
+        <v>1848.616</v>
       </c>
       <c r="G78">
         <v>111.7</v>
@@ -7683,28 +7683,28 @@
         <v>445.3</v>
       </c>
       <c r="M78">
-        <v>105.4623424</v>
+        <v>106.8500048</v>
       </c>
       <c r="N78">
-        <v>339.8376576</v>
+        <v>338.4499952</v>
       </c>
       <c r="O78">
-        <v>84.9594144</v>
+        <v>84.6124988</v>
       </c>
       <c r="P78">
-        <v>254.8782432</v>
+        <v>253.8374964</v>
       </c>
       <c r="Q78">
-        <v>393.6782432</v>
+        <v>392.6374964</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3969055268348008</v>
+        <v>0.4110402098796801</v>
       </c>
       <c r="T78">
-        <v>2.147317694847958</v>
+        <v>2.233763656798359</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.222360227037779</v>
+        <v>4.167524379933392</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1279187482723264</v>
+        <v>0.1276341701043006</v>
       </c>
       <c r="C79">
-        <v>1131.474501738796</v>
+        <v>1116.005667620472</v>
       </c>
       <c r="D79">
-        <v>2868.390501738796</v>
+        <v>2876.929667620473</v>
       </c>
       <c r="E79">
-        <v>1701.716</v>
+        <v>1725.724</v>
       </c>
       <c r="F79">
-        <v>1848.616</v>
+        <v>1872.624</v>
       </c>
       <c r="G79">
         <v>111.7</v>
@@ -7765,28 +7765,28 @@
         <v>445.3</v>
       </c>
       <c r="M79">
-        <v>106.8500048</v>
+        <v>108.2376672</v>
       </c>
       <c r="N79">
-        <v>338.4499952</v>
+        <v>337.0623328</v>
       </c>
       <c r="O79">
-        <v>84.6124988</v>
+        <v>84.26558319999999</v>
       </c>
       <c r="P79">
-        <v>253.8374964</v>
+        <v>252.7967496</v>
       </c>
       <c r="Q79">
-        <v>392.6374964</v>
+        <v>391.5967496</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4110402098796801</v>
+        <v>0.4264598641104575</v>
       </c>
       <c r="T79">
-        <v>2.233763656798359</v>
+        <v>2.328068342562433</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.167524379933392</v>
+        <v>4.114094580190656</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1276341701043006</v>
+        <v>0.1273495919362749</v>
       </c>
       <c r="C80">
-        <v>1116.005667620472</v>
+        <v>1100.587827309442</v>
       </c>
       <c r="D80">
-        <v>2876.929667620473</v>
+        <v>2885.519827309442</v>
       </c>
       <c r="E80">
-        <v>1725.724</v>
+        <v>1749.732</v>
       </c>
       <c r="F80">
-        <v>1872.624</v>
+        <v>1896.632</v>
       </c>
       <c r="G80">
         <v>111.7</v>
@@ -7847,28 +7847,28 @@
         <v>445.3</v>
       </c>
       <c r="M80">
-        <v>108.2376672</v>
+        <v>109.6253296</v>
       </c>
       <c r="N80">
-        <v>337.0623328</v>
+        <v>335.6746704</v>
       </c>
       <c r="O80">
-        <v>84.26558319999999</v>
+        <v>83.91866759999999</v>
       </c>
       <c r="P80">
-        <v>252.7967496</v>
+        <v>251.7560028</v>
       </c>
       <c r="Q80">
-        <v>391.5967496</v>
+        <v>390.5560028</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4264598641104575</v>
+        <v>0.4433480568394042</v>
       </c>
       <c r="T80">
-        <v>2.328068342562433</v>
+        <v>2.431354426970705</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.114094580190656</v>
+        <v>4.062017433605964</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1273495919362749</v>
+        <v>0.1270650137682491</v>
       </c>
       <c r="C81">
-        <v>1100.587827309442</v>
+        <v>1085.221438957484</v>
       </c>
       <c r="D81">
-        <v>2885.519827309442</v>
+        <v>2894.161438957485</v>
       </c>
       <c r="E81">
-        <v>1749.732</v>
+        <v>1773.74</v>
       </c>
       <c r="F81">
-        <v>1896.632</v>
+        <v>1920.64</v>
       </c>
       <c r="G81">
         <v>111.7</v>
@@ -7929,28 +7929,28 @@
         <v>445.3</v>
       </c>
       <c r="M81">
-        <v>109.6253296</v>
+        <v>111.012992</v>
       </c>
       <c r="N81">
-        <v>335.6746704</v>
+        <v>334.287008</v>
       </c>
       <c r="O81">
-        <v>83.91866759999999</v>
+        <v>83.571752</v>
       </c>
       <c r="P81">
-        <v>251.7560028</v>
+        <v>250.715256</v>
       </c>
       <c r="Q81">
-        <v>390.5560028</v>
+        <v>389.515256</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4433480568394042</v>
+        <v>0.4619250688412455</v>
       </c>
       <c r="T81">
-        <v>2.431354426970705</v>
+        <v>2.544969119819803</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.062017433605964</v>
+        <v>4.01124221568589</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1270650137682491</v>
+        <v>0.1289066856002233</v>
       </c>
       <c r="C82">
-        <v>1085.221438957484</v>
+        <v>1006.187499136892</v>
       </c>
       <c r="D82">
-        <v>2894.161438957485</v>
+        <v>2839.135499136892</v>
       </c>
       <c r="E82">
-        <v>1773.74</v>
+        <v>1797.748</v>
       </c>
       <c r="F82">
-        <v>1920.64</v>
+        <v>1944.648</v>
       </c>
       <c r="G82">
         <v>111.7</v>
@@ -8011,45 +8011,45 @@
         <v>445.3</v>
       </c>
       <c r="M82">
-        <v>111.012992</v>
+        <v>119.2069224</v>
       </c>
       <c r="N82">
-        <v>334.287008</v>
+        <v>326.0930776</v>
       </c>
       <c r="O82">
-        <v>83.571752</v>
+        <v>81.5232694</v>
       </c>
       <c r="P82">
-        <v>250.715256</v>
+        <v>244.5698082</v>
       </c>
       <c r="Q82">
-        <v>389.515256</v>
+        <v>383.3698082</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4619250688412455</v>
+        <v>0.4824575557906491</v>
       </c>
       <c r="T82">
-        <v>2.544969119819803</v>
+        <v>2.670543254021438</v>
       </c>
       <c r="U82">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.01124221568589</v>
+        <v>3.735521319020312</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1289066856002233</v>
+        <v>0.1286483574321975</v>
       </c>
       <c r="C83">
-        <v>1006.187499136892</v>
+        <v>989.7713927719619</v>
       </c>
       <c r="D83">
-        <v>2839.135499136892</v>
+        <v>2846.727392771963</v>
       </c>
       <c r="E83">
-        <v>1797.748</v>
+        <v>1821.756</v>
       </c>
       <c r="F83">
-        <v>1944.648</v>
+        <v>1968.656</v>
       </c>
       <c r="G83">
         <v>111.7</v>
@@ -8093,28 +8093,28 @@
         <v>445.3</v>
       </c>
       <c r="M83">
-        <v>119.2069224</v>
+        <v>120.6786128</v>
       </c>
       <c r="N83">
-        <v>326.0930776</v>
+        <v>324.6213872</v>
       </c>
       <c r="O83">
-        <v>81.5232694</v>
+        <v>81.15534679999999</v>
       </c>
       <c r="P83">
-        <v>244.5698082</v>
+        <v>243.4660404</v>
       </c>
       <c r="Q83">
-        <v>383.3698082</v>
+        <v>382.2660404</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4824575557906491</v>
+        <v>0.5052714301788752</v>
       </c>
       <c r="T83">
-        <v>2.670543254021438</v>
+        <v>2.810070069801033</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.735521319020312</v>
+        <v>3.689966180983478</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1286483574321975</v>
+        <v>0.1283900292641718</v>
       </c>
       <c r="C84">
-        <v>989.7713927719619</v>
+        <v>973.3959969571747</v>
       </c>
       <c r="D84">
-        <v>2846.727392771963</v>
+        <v>2854.359996957175</v>
       </c>
       <c r="E84">
-        <v>1821.756</v>
+        <v>1845.764</v>
       </c>
       <c r="F84">
-        <v>1968.656</v>
+        <v>1992.664</v>
       </c>
       <c r="G84">
         <v>111.7</v>
@@ -8175,28 +8175,28 @@
         <v>445.3</v>
       </c>
       <c r="M84">
-        <v>120.6786128</v>
+        <v>122.1503032</v>
       </c>
       <c r="N84">
-        <v>324.6213872</v>
+        <v>323.1496968</v>
       </c>
       <c r="O84">
-        <v>81.15534679999999</v>
+        <v>80.7874242</v>
       </c>
       <c r="P84">
-        <v>243.4660404</v>
+        <v>242.3622726</v>
       </c>
       <c r="Q84">
-        <v>382.2660404</v>
+        <v>381.1622726000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5052714301788752</v>
+        <v>0.5307692897892458</v>
       </c>
       <c r="T84">
-        <v>2.810070069801033</v>
+        <v>2.96601180508411</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.689966180983478</v>
+        <v>3.645508757116208</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1283900292641718</v>
+        <v>0.128131701096146</v>
       </c>
       <c r="C85">
-        <v>973.3959969571747</v>
+        <v>957.0616400304746</v>
       </c>
       <c r="D85">
-        <v>2854.359996957175</v>
+        <v>2862.033640030475</v>
       </c>
       <c r="E85">
-        <v>1845.764</v>
+        <v>1869.772</v>
       </c>
       <c r="F85">
-        <v>1992.664</v>
+        <v>2016.672</v>
       </c>
       <c r="G85">
         <v>111.7</v>
@@ -8257,28 +8257,28 @@
         <v>445.3</v>
       </c>
       <c r="M85">
-        <v>122.1503032</v>
+        <v>123.6219936</v>
       </c>
       <c r="N85">
-        <v>323.1496968</v>
+        <v>321.6780064</v>
       </c>
       <c r="O85">
-        <v>80.7874242</v>
+        <v>80.4195016</v>
       </c>
       <c r="P85">
-        <v>242.3622726</v>
+        <v>241.2585048</v>
       </c>
       <c r="Q85">
-        <v>381.1622726000001</v>
+        <v>380.0585048</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5307692897892458</v>
+        <v>0.5594543818509126</v>
       </c>
       <c r="T85">
-        <v>2.96601180508411</v>
+        <v>3.141446257277571</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.645508757116208</v>
+        <v>3.602109843341015</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.128131701096146</v>
+        <v>0.1278733729281202</v>
       </c>
       <c r="C86">
-        <v>957.0616400304748</v>
+        <v>940.7686538701289</v>
       </c>
       <c r="D86">
-        <v>2862.033640030475</v>
+        <v>2869.748653870129</v>
       </c>
       <c r="E86">
-        <v>1869.772</v>
+        <v>1893.78</v>
       </c>
       <c r="F86">
-        <v>2016.672</v>
+        <v>2040.68</v>
       </c>
       <c r="G86">
         <v>111.7</v>
@@ -8339,28 +8339,28 @@
         <v>445.3</v>
       </c>
       <c r="M86">
-        <v>123.6219936</v>
+        <v>125.093684</v>
       </c>
       <c r="N86">
-        <v>321.6780064</v>
+        <v>320.206316</v>
       </c>
       <c r="O86">
-        <v>80.4195016</v>
+        <v>80.051579</v>
       </c>
       <c r="P86">
-        <v>241.2585048</v>
+        <v>240.154737</v>
       </c>
       <c r="Q86">
-        <v>380.0585048</v>
+        <v>378.954737</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5594543818509122</v>
+        <v>0.5919641528541345</v>
       </c>
       <c r="T86">
-        <v>3.141446257277568</v>
+        <v>3.340271969763491</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.602109843341016</v>
+        <v>3.55973208047818</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1278733729281202</v>
+        <v>0.1276150447600944</v>
       </c>
       <c r="C87">
-        <v>940.7686538701289</v>
+        <v>924.5173739425777</v>
       </c>
       <c r="D87">
-        <v>2869.748653870129</v>
+        <v>2877.505373942578</v>
       </c>
       <c r="E87">
-        <v>1893.78</v>
+        <v>1917.788</v>
       </c>
       <c r="F87">
-        <v>2040.68</v>
+        <v>2064.688</v>
       </c>
       <c r="G87">
         <v>111.7</v>
@@ -8421,28 +8421,28 @@
         <v>445.3</v>
       </c>
       <c r="M87">
-        <v>125.093684</v>
+        <v>126.5653744</v>
       </c>
       <c r="N87">
-        <v>320.206316</v>
+        <v>318.7346256</v>
       </c>
       <c r="O87">
-        <v>80.051579</v>
+        <v>79.6836564</v>
       </c>
       <c r="P87">
-        <v>240.154737</v>
+        <v>239.0509692</v>
       </c>
       <c r="Q87">
-        <v>378.954737</v>
+        <v>377.8509692</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5919641528541345</v>
+        <v>0.6291181768578171</v>
       </c>
       <c r="T87">
-        <v>3.340271969763491</v>
+        <v>3.567501355461687</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.55973208047818</v>
+        <v>3.518339846984247</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1276150447600944</v>
+        <v>0.1291837165920686</v>
       </c>
       <c r="C88">
-        <v>924.5173739425777</v>
+        <v>854.0428251516832</v>
       </c>
       <c r="D88">
-        <v>2877.505373942578</v>
+        <v>2831.038825151684</v>
       </c>
       <c r="E88">
-        <v>1917.788</v>
+        <v>1941.796</v>
       </c>
       <c r="F88">
-        <v>2064.688</v>
+        <v>2088.696</v>
       </c>
       <c r="G88">
         <v>111.7</v>
@@ -8503,45 +8503,45 @@
         <v>445.3</v>
       </c>
       <c r="M88">
-        <v>126.5653744</v>
+        <v>133.8854136</v>
       </c>
       <c r="N88">
-        <v>318.7346256</v>
+        <v>311.4145864</v>
       </c>
       <c r="O88">
-        <v>79.6836564</v>
+        <v>77.85364659999999</v>
       </c>
       <c r="P88">
-        <v>239.0509692</v>
+        <v>233.5609398</v>
       </c>
       <c r="Q88">
-        <v>377.8509692</v>
+        <v>372.3609398</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6291181768578171</v>
+        <v>0.671988204554374</v>
       </c>
       <c r="T88">
-        <v>3.567501355461687</v>
+        <v>3.829689108190375</v>
       </c>
       <c r="U88">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.518339846984247</v>
+        <v>3.325978446990434</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1291837165920686</v>
+        <v>0.1289463884240429</v>
       </c>
       <c r="C89">
-        <v>854.0428251516832</v>
+        <v>836.9682787211686</v>
       </c>
       <c r="D89">
-        <v>2831.038825151684</v>
+        <v>2837.972278721169</v>
       </c>
       <c r="E89">
-        <v>1941.796</v>
+        <v>1965.804</v>
       </c>
       <c r="F89">
-        <v>2088.696</v>
+        <v>2112.704</v>
       </c>
       <c r="G89">
         <v>111.7</v>
@@ -8585,28 +8585,28 @@
         <v>445.3</v>
       </c>
       <c r="M89">
-        <v>133.8854136</v>
+        <v>135.4243264</v>
       </c>
       <c r="N89">
-        <v>311.4145864</v>
+        <v>309.8756736</v>
       </c>
       <c r="O89">
-        <v>77.85364659999999</v>
+        <v>77.46891840000001</v>
       </c>
       <c r="P89">
-        <v>233.5609398</v>
+        <v>232.4067552</v>
       </c>
       <c r="Q89">
-        <v>372.3609398</v>
+        <v>371.2067552</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.671988204554374</v>
+        <v>0.7220032368670238</v>
       </c>
       <c r="T89">
-        <v>3.829689108190375</v>
+        <v>4.13557481970718</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.325978446990434</v>
+        <v>3.288183237365543</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1289463884240429</v>
+        <v>0.1287090602560171</v>
       </c>
       <c r="C90">
-        <v>836.9682787211686</v>
+        <v>819.9277768974057</v>
       </c>
       <c r="D90">
-        <v>2837.972278721169</v>
+        <v>2844.939776897406</v>
       </c>
       <c r="E90">
-        <v>1965.804</v>
+        <v>1989.812</v>
       </c>
       <c r="F90">
-        <v>2112.704</v>
+        <v>2136.712</v>
       </c>
       <c r="G90">
         <v>111.7</v>
@@ -8667,28 +8667,28 @@
         <v>445.3</v>
       </c>
       <c r="M90">
-        <v>135.4243264</v>
+        <v>136.9632392</v>
       </c>
       <c r="N90">
-        <v>309.8756736</v>
+        <v>308.3367608</v>
       </c>
       <c r="O90">
-        <v>77.46891840000001</v>
+        <v>77.08419019999999</v>
       </c>
       <c r="P90">
-        <v>232.4067552</v>
+        <v>231.2525706</v>
       </c>
       <c r="Q90">
-        <v>371.2067552</v>
+        <v>370.0525706</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7220032368670238</v>
+        <v>0.7811119114183371</v>
       </c>
       <c r="T90">
-        <v>4.13557481970718</v>
+        <v>4.497076115136129</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.288183237365543</v>
+        <v>3.25123735829402</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1287090602560171</v>
+        <v>0.1284717320879913</v>
       </c>
       <c r="C91">
-        <v>819.9277768974057</v>
+        <v>802.9215710459907</v>
       </c>
       <c r="D91">
-        <v>2844.939776897406</v>
+        <v>2851.941571045991</v>
       </c>
       <c r="E91">
-        <v>1989.812</v>
+        <v>2013.82</v>
       </c>
       <c r="F91">
-        <v>2136.712</v>
+        <v>2160.72</v>
       </c>
       <c r="G91">
         <v>111.7</v>
@@ -8749,28 +8749,28 @@
         <v>445.3</v>
       </c>
       <c r="M91">
-        <v>136.9632392</v>
+        <v>138.502152</v>
       </c>
       <c r="N91">
-        <v>308.3367608</v>
+        <v>306.797848</v>
       </c>
       <c r="O91">
-        <v>77.08419019999999</v>
+        <v>76.699462</v>
       </c>
       <c r="P91">
-        <v>231.2525706</v>
+        <v>230.098386</v>
       </c>
       <c r="Q91">
-        <v>370.0525706</v>
+        <v>368.898386</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7811119114183371</v>
+        <v>0.8520423208799132</v>
       </c>
       <c r="T91">
-        <v>4.497076115136129</v>
+        <v>4.930877669650869</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.25123735829402</v>
+        <v>3.21511249875742</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1284717320879913</v>
+        <v>0.1282344039199655</v>
       </c>
       <c r="C92">
-        <v>802.9215710459907</v>
+        <v>785.949915013211</v>
       </c>
       <c r="D92">
-        <v>2851.941571045991</v>
+        <v>2858.977915013211</v>
       </c>
       <c r="E92">
-        <v>2013.82</v>
+        <v>2037.828</v>
       </c>
       <c r="F92">
-        <v>2160.72</v>
+        <v>2184.728</v>
       </c>
       <c r="G92">
         <v>111.7</v>
@@ -8831,28 +8831,28 @@
         <v>445.3</v>
       </c>
       <c r="M92">
-        <v>138.502152</v>
+        <v>140.0410648</v>
       </c>
       <c r="N92">
-        <v>306.797848</v>
+        <v>305.2589352</v>
       </c>
       <c r="O92">
-        <v>76.699462</v>
+        <v>76.3147338</v>
       </c>
       <c r="P92">
-        <v>230.098386</v>
+        <v>228.9442014</v>
       </c>
       <c r="Q92">
-        <v>368.898386</v>
+        <v>367.7442014</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8520423208799132</v>
+        <v>0.9387350435551727</v>
       </c>
       <c r="T92">
-        <v>4.930877669650869</v>
+        <v>5.461079569613328</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.21511249875742</v>
+        <v>3.179781592177668</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1282344039199655</v>
+        <v>0.1279970757519397</v>
       </c>
       <c r="C93">
-        <v>785.949915013211</v>
+        <v>769.013065156716</v>
       </c>
       <c r="D93">
-        <v>2858.977915013211</v>
+        <v>2866.049065156717</v>
       </c>
       <c r="E93">
-        <v>2037.828</v>
+        <v>2061.836</v>
       </c>
       <c r="F93">
-        <v>2184.728</v>
+        <v>2208.736</v>
       </c>
       <c r="G93">
         <v>111.7</v>
@@ -8913,28 +8913,28 @@
         <v>445.3</v>
       </c>
       <c r="M93">
-        <v>140.0410648</v>
+        <v>141.5799776</v>
       </c>
       <c r="N93">
-        <v>305.2589352</v>
+        <v>303.7200223999999</v>
       </c>
       <c r="O93">
-        <v>76.3147338</v>
+        <v>75.93000559999999</v>
       </c>
       <c r="P93">
-        <v>228.9442014</v>
+        <v>227.7900168</v>
       </c>
       <c r="Q93">
-        <v>367.7442014</v>
+        <v>366.5900167999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9387350435551727</v>
+        <v>1.047100946899247</v>
       </c>
       <c r="T93">
-        <v>5.461079569613328</v>
+        <v>6.123831944566403</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.179781592177668</v>
+        <v>3.145218748784432</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1279970757519397</v>
+        <v>0.127759747583914</v>
       </c>
       <c r="C94">
-        <v>769.013065156716</v>
+        <v>752.1112803766591</v>
       </c>
       <c r="D94">
-        <v>2866.049065156717</v>
+        <v>2873.155280376659</v>
       </c>
       <c r="E94">
-        <v>2061.836</v>
+        <v>2085.844</v>
       </c>
       <c r="F94">
-        <v>2208.736</v>
+        <v>2232.744</v>
       </c>
       <c r="G94">
         <v>111.7</v>
@@ -8995,28 +8995,28 @@
         <v>445.3</v>
       </c>
       <c r="M94">
-        <v>141.5799776</v>
+        <v>143.1188904</v>
       </c>
       <c r="N94">
-        <v>303.7200223999999</v>
+        <v>302.1811096</v>
       </c>
       <c r="O94">
-        <v>75.93000559999999</v>
+        <v>75.5452774</v>
       </c>
       <c r="P94">
-        <v>227.7900168</v>
+        <v>226.6358322</v>
       </c>
       <c r="Q94">
-        <v>366.5900167999999</v>
+        <v>365.4358322</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.047100946899247</v>
+        <v>1.186428536913058</v>
       </c>
       <c r="T94">
-        <v>6.123831944566403</v>
+        <v>6.975942140934642</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.145218748784432</v>
+        <v>3.11139919234589</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.127759747583914</v>
+        <v>0.1275224194158882</v>
       </c>
       <c r="C95">
-        <v>752.1112803766591</v>
+        <v>735.244822147291</v>
       </c>
       <c r="D95">
-        <v>2873.155280376659</v>
+        <v>2880.296822147292</v>
       </c>
       <c r="E95">
-        <v>2085.844</v>
+        <v>2109.852</v>
       </c>
       <c r="F95">
-        <v>2232.744</v>
+        <v>2256.752</v>
       </c>
       <c r="G95">
         <v>111.7</v>
@@ -9077,28 +9077,28 @@
         <v>445.3</v>
       </c>
       <c r="M95">
-        <v>143.1188904</v>
+        <v>144.6578032</v>
       </c>
       <c r="N95">
-        <v>302.1811096</v>
+        <v>300.6421968</v>
       </c>
       <c r="O95">
-        <v>75.5452774</v>
+        <v>75.16054919999999</v>
       </c>
       <c r="P95">
-        <v>226.6358322</v>
+        <v>225.4816476</v>
       </c>
       <c r="Q95">
-        <v>365.4358322</v>
+        <v>364.2816476</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.186428536913058</v>
+        <v>1.372198656931471</v>
       </c>
       <c r="T95">
-        <v>6.975942140934642</v>
+        <v>8.112089069425627</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.11139919234589</v>
+        <v>3.078299200937955</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1275224194158882</v>
+        <v>0.1272850912478624</v>
       </c>
       <c r="C96">
-        <v>735.244822147291</v>
+        <v>718.4139545490316</v>
       </c>
       <c r="D96">
-        <v>2880.296822147292</v>
+        <v>2887.473954549032</v>
       </c>
       <c r="E96">
-        <v>2109.852</v>
+        <v>2133.86</v>
       </c>
       <c r="F96">
-        <v>2256.752</v>
+        <v>2280.76</v>
       </c>
       <c r="G96">
         <v>111.7</v>
@@ -9159,28 +9159,28 @@
         <v>445.3</v>
       </c>
       <c r="M96">
-        <v>144.6578032</v>
+        <v>146.196716</v>
       </c>
       <c r="N96">
-        <v>300.6421968</v>
+        <v>299.103284</v>
       </c>
       <c r="O96">
-        <v>75.16054919999999</v>
+        <v>74.77582099999999</v>
       </c>
       <c r="P96">
-        <v>225.4816476</v>
+        <v>224.327463</v>
       </c>
       <c r="Q96">
-        <v>364.2816476</v>
+        <v>363.127463</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.372198656931471</v>
+        <v>1.63227682495725</v>
       </c>
       <c r="T96">
-        <v>8.112089069425627</v>
+        <v>9.702694769313011</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.078299200937955</v>
+        <v>3.045896051454397</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1272850912478624</v>
+        <v>0.1270477630798366</v>
       </c>
       <c r="C97">
-        <v>718.4139545490316</v>
+        <v>701.6189443010221</v>
       </c>
       <c r="D97">
-        <v>2887.473954549032</v>
+        <v>2894.686944301023</v>
       </c>
       <c r="E97">
-        <v>2133.86</v>
+        <v>2157.868</v>
       </c>
       <c r="F97">
-        <v>2280.76</v>
+        <v>2304.768</v>
       </c>
       <c r="G97">
         <v>111.7</v>
@@ -9241,28 +9241,28 @@
         <v>445.3</v>
       </c>
       <c r="M97">
-        <v>146.196716</v>
+        <v>147.7356288</v>
       </c>
       <c r="N97">
-        <v>299.103284</v>
+        <v>297.5643712</v>
       </c>
       <c r="O97">
-        <v>74.77582099999999</v>
+        <v>74.3910928</v>
       </c>
       <c r="P97">
-        <v>224.327463</v>
+        <v>223.1732784</v>
       </c>
       <c r="Q97">
-        <v>363.127463</v>
+        <v>361.9732784</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.63227682495725</v>
+        <v>2.022394076995919</v>
       </c>
       <c r="T97">
-        <v>9.702694769313011</v>
+        <v>12.08860331914408</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.045896051454397</v>
+        <v>3.014167967585081</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1270477630798366</v>
+        <v>0.1324849349118108</v>
       </c>
       <c r="C98">
-        <v>701.6189443010221</v>
+        <v>520.9166137460429</v>
       </c>
       <c r="D98">
-        <v>2894.686944301022</v>
+        <v>2737.992613746043</v>
       </c>
       <c r="E98">
-        <v>2157.868</v>
+        <v>2181.876</v>
       </c>
       <c r="F98">
-        <v>2304.768</v>
+        <v>2328.776</v>
       </c>
       <c r="G98">
         <v>111.7</v>
@@ -9323,45 +9323,45 @@
         <v>445.3</v>
       </c>
       <c r="M98">
-        <v>147.7356288</v>
+        <v>167.4389944</v>
       </c>
       <c r="N98">
-        <v>297.5643712</v>
+        <v>277.8610056</v>
       </c>
       <c r="O98">
-        <v>74.3910928</v>
+        <v>69.4652514</v>
       </c>
       <c r="P98">
-        <v>223.1732784</v>
+        <v>208.3957542</v>
       </c>
       <c r="Q98">
-        <v>361.9732784</v>
+        <v>347.1957542</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.022394076995914</v>
+        <v>2.672589497060359</v>
       </c>
       <c r="T98">
-        <v>12.08860331914405</v>
+        <v>16.06511756886249</v>
       </c>
       <c r="U98">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.014167967585081</v>
+        <v>2.659476077216574</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1324849349118108</v>
+        <v>0.1323061067437851</v>
       </c>
       <c r="C99">
-        <v>520.9166137460429</v>
+        <v>501.791996037332</v>
       </c>
       <c r="D99">
-        <v>2737.992613746043</v>
+        <v>2742.875996037332</v>
       </c>
       <c r="E99">
-        <v>2181.876</v>
+        <v>2205.884</v>
       </c>
       <c r="F99">
-        <v>2328.776</v>
+        <v>2352.784</v>
       </c>
       <c r="G99">
         <v>111.7</v>
@@ -9405,28 +9405,28 @@
         <v>445.3</v>
       </c>
       <c r="M99">
-        <v>167.4389944</v>
+        <v>169.1651696</v>
       </c>
       <c r="N99">
-        <v>277.8610056</v>
+        <v>276.1348304</v>
       </c>
       <c r="O99">
-        <v>69.4652514</v>
+        <v>69.0337076</v>
       </c>
       <c r="P99">
-        <v>208.3957542</v>
+        <v>207.1011228</v>
       </c>
       <c r="Q99">
-        <v>347.1957542</v>
+        <v>345.9011228</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.672589497060359</v>
+        <v>3.97298033718925</v>
       </c>
       <c r="T99">
-        <v>16.06511756886249</v>
+        <v>24.01814606829937</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.659476077216574</v>
+        <v>2.632338566224568</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1323061067437851</v>
+        <v>0.1321272785757593</v>
       </c>
       <c r="C100">
-        <v>501.791996037332</v>
+        <v>482.6848290929929</v>
       </c>
       <c r="D100">
-        <v>2742.875996037332</v>
+        <v>2747.776829092993</v>
       </c>
       <c r="E100">
-        <v>2205.884</v>
+        <v>2229.892</v>
       </c>
       <c r="F100">
-        <v>2352.784</v>
+        <v>2376.792</v>
       </c>
       <c r="G100">
         <v>111.7</v>
@@ -9487,28 +9487,28 @@
         <v>445.3</v>
       </c>
       <c r="M100">
-        <v>169.1651696</v>
+        <v>170.8913448</v>
       </c>
       <c r="N100">
-        <v>276.1348304</v>
+        <v>274.4086552</v>
       </c>
       <c r="O100">
-        <v>69.0337076</v>
+        <v>68.6021638</v>
       </c>
       <c r="P100">
-        <v>207.1011228</v>
+        <v>205.8064914</v>
       </c>
       <c r="Q100">
-        <v>345.9011228</v>
+        <v>344.6064914</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.97298033718925</v>
+        <v>7.874152857575924</v>
       </c>
       <c r="T100">
-        <v>24.01814606829937</v>
+        <v>47.87723156661</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.632338566224568</v>
+        <v>2.605749287777855</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1321272785757593</v>
-      </c>
-      <c r="C101">
-        <v>482.6848290929929</v>
-      </c>
-      <c r="D101">
-        <v>2747.776829092993</v>
-      </c>
-      <c r="E101">
-        <v>2229.892</v>
-      </c>
-      <c r="F101">
-        <v>2376.792</v>
-      </c>
-      <c r="G101">
-        <v>111.7</v>
-      </c>
-      <c r="H101">
-        <v>2253.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>584.1</v>
-      </c>
-      <c r="K101">
-        <v>138.8</v>
-      </c>
-      <c r="L101">
-        <v>445.3</v>
-      </c>
-      <c r="M101">
-        <v>170.8913448</v>
-      </c>
-      <c r="N101">
-        <v>274.4086552</v>
-      </c>
-      <c r="O101">
-        <v>68.6021638</v>
-      </c>
-      <c r="P101">
-        <v>205.8064914</v>
-      </c>
-      <c r="Q101">
-        <v>344.6064914</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.874152857575924</v>
-      </c>
-      <c r="T101">
-        <v>47.87723156661</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.053925</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.605749287777855</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
